--- a/Scout/waukee-vs-ankeny-090426.xlsx
+++ b/Scout/waukee-vs-ankeny-090426.xlsx
@@ -5,7 +5,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="Rdecdc58565dc40b0"/>
+    <sheet name="Sheet1" sheetId="1" r:id="Rfc8c05187c204f75"/>
   </sheets>
 </workbook>
 </file>
@@ -58,6 +58,21 @@
     <t>PASS ZONE</t>
   </si>
   <si>
+    <t>BACKFIELD</t>
+  </si>
+  <si>
+    <t>DEF FRONT</t>
+  </si>
+  <si>
+    <t>FRONT MOVEMENT</t>
+  </si>
+  <si>
+    <t>COVERAGE</t>
+  </si>
+  <si>
+    <t>BLITZ</t>
+  </si>
+  <si>
     <t>KICK YARDS</t>
   </si>
   <si>
@@ -79,9 +94,6 @@
     <t>MOTION DIR</t>
   </si>
   <si>
-    <t>COVERAGE</t>
-  </si>
-  <si>
     <t>SERIES</t>
   </si>
   <si>
@@ -112,6 +124,9 @@
     <t>Y</t>
   </si>
   <si>
+    <t>G</t>
+  </si>
+  <si>
     <t>R</t>
   </si>
   <si>
@@ -130,6 +145,9 @@
     <t>N</t>
   </si>
   <si>
+    <t>Q</t>
+  </si>
+  <si>
     <t>EMPTY</t>
   </si>
   <si>
@@ -142,6 +160,9 @@
     <t>Penalty</t>
   </si>
   <si>
+    <t>GUN</t>
+  </si>
+  <si>
     <t>BAL</t>
   </si>
   <si>
@@ -166,6 +187,9 @@
     <t>GIVE @1</t>
   </si>
   <si>
+    <t>G K DOT</t>
+  </si>
+  <si>
     <t>CLOSED</t>
   </si>
   <si>
@@ -187,6 +211,12 @@
     <t>Fair Catch</t>
   </si>
   <si>
+    <t>GUN EVEN</t>
+  </si>
+  <si>
+    <t>G GUN</t>
+  </si>
+  <si>
     <t>TRIPS</t>
   </si>
   <si>
@@ -199,6 +229,9 @@
     <t>VERTICAL</t>
   </si>
   <si>
+    <t>DOT</t>
+  </si>
+  <si>
     <t>POWER</t>
   </si>
   <si>
@@ -215,6 +248,9 @@
   </si>
   <si>
     <t>TWINS WING</t>
+  </si>
+  <si>
+    <t>K TUCK G</t>
   </si>
   <si>
     <t>TWINS OPEN</t>
@@ -311,7 +347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y145"/>
+  <dimension ref="A1:AC145"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -389,6 +425,18 @@
       <c r="Y1" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -398,19 +446,19 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F2">
         <v>-40</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -421,7 +469,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -433,30 +481,33 @@
         <v>-30</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J3">
         <v>-1</v>
       </c>
       <c r="K3" t="s">
-        <v>32</v>
-      </c>
-      <c r="R3" t="s">
-        <v>33</v>
-      </c>
-      <c r="S3" t="s">
-        <v>34</v>
-      </c>
-      <c r="U3" t="s">
-        <v>33</v>
-      </c>
-      <c r="X3">
+        <v>36</v>
+      </c>
+      <c r="P3" t="s">
+        <v>37</v>
+      </c>
+      <c r="W3" t="s">
+        <v>38</v>
+      </c>
+      <c r="X3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB3">
         <v>1</v>
       </c>
     </row>
@@ -468,7 +519,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -480,30 +531,33 @@
         <v>-29</v>
       </c>
       <c r="G4" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J4">
         <v>5</v>
       </c>
       <c r="K4" t="s">
-        <v>32</v>
-      </c>
-      <c r="R4" t="s">
-        <v>33</v>
-      </c>
-      <c r="S4" t="s">
-        <v>35</v>
-      </c>
-      <c r="U4" t="s">
-        <v>33</v>
-      </c>
-      <c r="X4">
+        <v>36</v>
+      </c>
+      <c r="P4" t="s">
+        <v>29</v>
+      </c>
+      <c r="W4" t="s">
+        <v>38</v>
+      </c>
+      <c r="X4" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB4">
         <v>1</v>
       </c>
     </row>
@@ -515,7 +569,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -527,33 +581,36 @@
         <v>-34</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J5">
         <v>13</v>
       </c>
       <c r="K5" t="s">
-        <v>38</v>
-      </c>
-      <c r="R5" t="s">
-        <v>26</v>
-      </c>
-      <c r="S5" t="s">
-        <v>39</v>
-      </c>
-      <c r="U5" t="s">
-        <v>26</v>
-      </c>
-      <c r="V5" t="s">
-        <v>33</v>
-      </c>
-      <c r="X5">
+        <v>43</v>
+      </c>
+      <c r="P5" t="s">
+        <v>44</v>
+      </c>
+      <c r="W5" t="s">
+        <v>30</v>
+      </c>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB5">
         <v>1</v>
       </c>
     </row>
@@ -565,7 +622,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -577,24 +634,24 @@
         <v>-47</v>
       </c>
       <c r="G6" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J6">
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>32</v>
-      </c>
-      <c r="U6" t="s">
-        <v>33</v>
-      </c>
-      <c r="X6">
+        <v>36</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB6">
         <v>1</v>
       </c>
     </row>
@@ -606,7 +663,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -618,30 +675,33 @@
         <v>-49</v>
       </c>
       <c r="G7" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H7" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I7" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R7" t="s">
-        <v>33</v>
-      </c>
-      <c r="S7" t="s">
-        <v>35</v>
-      </c>
-      <c r="U7" t="s">
-        <v>33</v>
-      </c>
-      <c r="X7">
+        <v>36</v>
+      </c>
+      <c r="P7" t="s">
+        <v>37</v>
+      </c>
+      <c r="W7" t="s">
+        <v>38</v>
+      </c>
+      <c r="X7" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB7">
         <v>1</v>
       </c>
     </row>
@@ -653,7 +713,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D8">
         <v>3</v>
@@ -665,30 +725,33 @@
         <v>-49</v>
       </c>
       <c r="G8" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H8" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I8" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J8">
         <v>-10</v>
       </c>
       <c r="K8" t="s">
-        <v>32</v>
-      </c>
-      <c r="R8" t="s">
-        <v>43</v>
-      </c>
-      <c r="S8" t="s">
-        <v>44</v>
-      </c>
-      <c r="U8" t="s">
-        <v>33</v>
-      </c>
-      <c r="X8">
+        <v>36</v>
+      </c>
+      <c r="P8" t="s">
+        <v>49</v>
+      </c>
+      <c r="W8" t="s">
+        <v>50</v>
+      </c>
+      <c r="X8" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB8">
         <v>1</v>
       </c>
     </row>
@@ -700,7 +763,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D9">
         <v>3</v>
@@ -712,30 +775,33 @@
         <v>-39</v>
       </c>
       <c r="G9" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H9" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I9" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>32</v>
-      </c>
-      <c r="R9" t="s">
-        <v>43</v>
-      </c>
-      <c r="S9" t="s">
-        <v>44</v>
-      </c>
-      <c r="U9" t="s">
-        <v>26</v>
-      </c>
-      <c r="X9">
+        <v>36</v>
+      </c>
+      <c r="P9" t="s">
+        <v>49</v>
+      </c>
+      <c r="W9" t="s">
+        <v>50</v>
+      </c>
+      <c r="X9" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB9">
         <v>1</v>
       </c>
     </row>
@@ -747,7 +813,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D10">
         <v>4</v>
@@ -759,15 +825,15 @@
         <v>-39</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H10" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="I10" t="s">
-        <v>28</v>
-      </c>
-      <c r="X10">
+        <v>32</v>
+      </c>
+      <c r="AB10">
         <v>1</v>
       </c>
     </row>
@@ -779,7 +845,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -791,33 +857,36 @@
         <v>-45</v>
       </c>
       <c r="G11" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>38</v>
-      </c>
-      <c r="R11" t="s">
-        <v>33</v>
-      </c>
-      <c r="S11" t="s">
-        <v>34</v>
-      </c>
-      <c r="T11" t="s">
-        <v>47</v>
-      </c>
-      <c r="U11" t="s">
-        <v>33</v>
-      </c>
-      <c r="X11">
+        <v>43</v>
+      </c>
+      <c r="P11" t="s">
+        <v>29</v>
+      </c>
+      <c r="W11" t="s">
+        <v>38</v>
+      </c>
+      <c r="X11" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB11">
         <v>1</v>
       </c>
     </row>
@@ -829,7 +898,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -841,36 +910,39 @@
         <v>-45</v>
       </c>
       <c r="G12" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H12" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I12" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J12">
         <v>9</v>
       </c>
       <c r="K12" t="s">
-        <v>32</v>
-      </c>
-      <c r="R12" t="s">
-        <v>33</v>
-      </c>
-      <c r="S12" t="s">
-        <v>34</v>
-      </c>
-      <c r="T12" t="s">
-        <v>48</v>
-      </c>
-      <c r="U12" t="s">
-        <v>33</v>
-      </c>
-      <c r="V12" t="s">
-        <v>33</v>
-      </c>
-      <c r="X12">
+        <v>36</v>
+      </c>
+      <c r="P12" t="s">
+        <v>37</v>
+      </c>
+      <c r="W12" t="s">
+        <v>38</v>
+      </c>
+      <c r="X12" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB12">
         <v>1</v>
       </c>
     </row>
@@ -882,7 +954,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D13">
         <v>3</v>
@@ -894,33 +966,36 @@
         <v>46</v>
       </c>
       <c r="G13" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H13" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I13" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J13">
         <v>-3</v>
       </c>
       <c r="K13" t="s">
-        <v>38</v>
-      </c>
-      <c r="R13" t="s">
-        <v>26</v>
-      </c>
-      <c r="S13" t="s">
-        <v>49</v>
-      </c>
-      <c r="T13" t="s">
-        <v>50</v>
-      </c>
-      <c r="U13" t="s">
-        <v>26</v>
-      </c>
-      <c r="X13">
+        <v>43</v>
+      </c>
+      <c r="P13" t="s">
+        <v>29</v>
+      </c>
+      <c r="W13" t="s">
+        <v>30</v>
+      </c>
+      <c r="X13" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB13">
         <v>1</v>
       </c>
     </row>
@@ -932,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D14">
         <v>4</v>
@@ -944,24 +1019,27 @@
         <v>49</v>
       </c>
       <c r="G14" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I14" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J14">
         <v>-5</v>
       </c>
       <c r="K14" t="s">
-        <v>38</v>
-      </c>
-      <c r="R14" t="s">
         <v>43</v>
       </c>
-      <c r="S14" t="s">
-        <v>51</v>
-      </c>
-      <c r="X14">
+      <c r="P14" t="s">
+        <v>58</v>
+      </c>
+      <c r="W14" t="s">
+        <v>50</v>
+      </c>
+      <c r="X14" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB14">
         <v>1</v>
       </c>
     </row>
@@ -973,7 +1051,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -985,36 +1063,39 @@
         <v>49</v>
       </c>
       <c r="G15" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H15" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I15" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J15">
         <v>9</v>
       </c>
       <c r="K15" t="s">
-        <v>32</v>
-      </c>
-      <c r="R15" t="s">
-        <v>33</v>
-      </c>
-      <c r="S15" t="s">
-        <v>34</v>
-      </c>
-      <c r="T15" t="s">
-        <v>48</v>
-      </c>
-      <c r="U15" t="s">
-        <v>33</v>
-      </c>
-      <c r="V15" t="s">
-        <v>33</v>
-      </c>
-      <c r="X15">
+        <v>36</v>
+      </c>
+      <c r="P15" t="s">
+        <v>29</v>
+      </c>
+      <c r="W15" t="s">
+        <v>38</v>
+      </c>
+      <c r="X15" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB15">
         <v>1</v>
       </c>
     </row>
@@ -1026,7 +1107,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -1038,33 +1119,36 @@
         <v>40</v>
       </c>
       <c r="G16" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H16" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I16" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J16">
         <v>-10</v>
       </c>
       <c r="K16" t="s">
-        <v>38</v>
-      </c>
-      <c r="R16" t="s">
-        <v>26</v>
-      </c>
-      <c r="S16" t="s">
-        <v>52</v>
-      </c>
-      <c r="T16" t="s">
-        <v>53</v>
-      </c>
-      <c r="U16" t="s">
-        <v>26</v>
-      </c>
-      <c r="X16">
+        <v>43</v>
+      </c>
+      <c r="P16" t="s">
+        <v>29</v>
+      </c>
+      <c r="W16" t="s">
+        <v>30</v>
+      </c>
+      <c r="X16" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB16">
         <v>1</v>
       </c>
     </row>
@@ -1076,7 +1160,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -1088,33 +1172,36 @@
         <v>50</v>
       </c>
       <c r="G17" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H17" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I17" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J17">
         <v>-1</v>
       </c>
       <c r="K17" t="s">
-        <v>38</v>
-      </c>
-      <c r="R17" t="s">
-        <v>26</v>
-      </c>
-      <c r="S17" t="s">
-        <v>35</v>
-      </c>
-      <c r="T17" t="s">
-        <v>54</v>
-      </c>
-      <c r="U17" t="s">
-        <v>33</v>
-      </c>
-      <c r="X17">
+        <v>43</v>
+      </c>
+      <c r="P17" t="s">
+        <v>29</v>
+      </c>
+      <c r="W17" t="s">
+        <v>30</v>
+      </c>
+      <c r="X17" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB17">
         <v>1</v>
       </c>
     </row>
@@ -1126,7 +1213,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D18">
         <v>4</v>
@@ -1138,33 +1225,36 @@
         <v>-49</v>
       </c>
       <c r="G18" t="s">
+        <v>46</v>
+      </c>
+      <c r="H18" t="s">
+        <v>41</v>
+      </c>
+      <c r="I18" t="s">
+        <v>42</v>
+      </c>
+      <c r="J18">
+        <v>4</v>
+      </c>
+      <c r="K18" t="s">
+        <v>43</v>
+      </c>
+      <c r="P18" t="s">
+        <v>37</v>
+      </c>
+      <c r="W18" t="s">
+        <v>38</v>
+      </c>
+      <c r="X18" t="s">
         <v>40</v>
       </c>
-      <c r="H18" t="s">
-        <v>36</v>
-      </c>
-      <c r="I18" t="s">
-        <v>37</v>
-      </c>
-      <c r="J18">
-        <v>4</v>
-      </c>
-      <c r="K18" t="s">
-        <v>38</v>
-      </c>
-      <c r="R18" t="s">
-        <v>33</v>
-      </c>
-      <c r="S18" t="s">
-        <v>35</v>
-      </c>
-      <c r="T18" t="s">
-        <v>55</v>
-      </c>
-      <c r="U18" t="s">
-        <v>26</v>
-      </c>
-      <c r="X18">
+      <c r="Y18" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB18">
         <v>1</v>
       </c>
     </row>
@@ -1176,7 +1266,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -1188,15 +1278,15 @@
         <v>47</v>
       </c>
       <c r="G19" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H19" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="I19" t="s">
-        <v>57</v>
-      </c>
-      <c r="X19">
+        <v>65</v>
+      </c>
+      <c r="AB19">
         <v>1</v>
       </c>
     </row>
@@ -1208,7 +1298,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -1220,30 +1310,33 @@
         <v>-8</v>
       </c>
       <c r="G20" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H20" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I20" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J20">
         <v>-10</v>
       </c>
       <c r="K20" t="s">
-        <v>32</v>
-      </c>
-      <c r="R20" t="s">
-        <v>26</v>
-      </c>
-      <c r="S20" t="s">
-        <v>51</v>
-      </c>
-      <c r="U20" t="s">
-        <v>26</v>
-      </c>
-      <c r="X20">
+        <v>36</v>
+      </c>
+      <c r="P20" t="s">
+        <v>66</v>
+      </c>
+      <c r="W20" t="s">
+        <v>30</v>
+      </c>
+      <c r="X20" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB20">
         <v>2</v>
       </c>
     </row>
@@ -1255,7 +1348,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D21">
         <v>2</v>
@@ -1267,24 +1360,24 @@
         <v>-6</v>
       </c>
       <c r="G21" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H21" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I21" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>32</v>
-      </c>
-      <c r="U21" t="s">
-        <v>26</v>
-      </c>
-      <c r="X21">
+        <v>36</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB21">
         <v>2</v>
       </c>
     </row>
@@ -1296,7 +1389,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D22">
         <v>3</v>
@@ -1308,33 +1401,36 @@
         <v>-6</v>
       </c>
       <c r="G22" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H22" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I22" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J22">
         <v>6</v>
       </c>
       <c r="K22" t="s">
-        <v>32</v>
-      </c>
-      <c r="R22" t="s">
-        <v>33</v>
-      </c>
-      <c r="S22" t="s">
-        <v>58</v>
-      </c>
-      <c r="U22" t="s">
-        <v>33</v>
-      </c>
-      <c r="V22" t="s">
-        <v>26</v>
-      </c>
-      <c r="X22">
+        <v>36</v>
+      </c>
+      <c r="P22" t="s">
+        <v>67</v>
+      </c>
+      <c r="W22" t="s">
+        <v>38</v>
+      </c>
+      <c r="X22" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB22">
         <v>2</v>
       </c>
     </row>
@@ -1346,7 +1442,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D23">
         <v>4</v>
@@ -1358,15 +1454,15 @@
         <v>-12</v>
       </c>
       <c r="G23" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H23" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="I23" t="s">
-        <v>28</v>
-      </c>
-      <c r="X23">
+        <v>32</v>
+      </c>
+      <c r="AB23">
         <v>2</v>
       </c>
     </row>
@@ -1378,7 +1474,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -1390,36 +1486,39 @@
         <v>38</v>
       </c>
       <c r="G24" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H24" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I24" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J24">
         <v>8</v>
       </c>
       <c r="K24" t="s">
-        <v>32</v>
-      </c>
-      <c r="R24" t="s">
-        <v>26</v>
-      </c>
-      <c r="S24" t="s">
-        <v>52</v>
-      </c>
-      <c r="T24" t="s">
-        <v>59</v>
-      </c>
-      <c r="U24" t="s">
-        <v>26</v>
-      </c>
-      <c r="V24" t="s">
-        <v>33</v>
-      </c>
-      <c r="X24">
+        <v>36</v>
+      </c>
+      <c r="P24" t="s">
+        <v>37</v>
+      </c>
+      <c r="W24" t="s">
+        <v>30</v>
+      </c>
+      <c r="X24" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB24">
         <v>2</v>
       </c>
     </row>
@@ -1431,7 +1530,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D25">
         <v>2</v>
@@ -1443,33 +1542,36 @@
         <v>30</v>
       </c>
       <c r="G25" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H25" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I25" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>38</v>
-      </c>
-      <c r="R25" t="s">
-        <v>26</v>
-      </c>
-      <c r="S25" t="s">
-        <v>35</v>
-      </c>
-      <c r="T25" t="s">
-        <v>60</v>
-      </c>
-      <c r="U25" t="s">
-        <v>26</v>
-      </c>
-      <c r="X25">
+        <v>43</v>
+      </c>
+      <c r="P25" t="s">
+        <v>29</v>
+      </c>
+      <c r="W25" t="s">
+        <v>30</v>
+      </c>
+      <c r="X25" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB25">
         <v>2</v>
       </c>
     </row>
@@ -1481,7 +1583,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D26">
         <v>3</v>
@@ -1493,33 +1595,36 @@
         <v>30</v>
       </c>
       <c r="G26" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H26" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I26" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>38</v>
-      </c>
-      <c r="R26" t="s">
-        <v>33</v>
-      </c>
-      <c r="S26" t="s">
-        <v>35</v>
-      </c>
-      <c r="T26" t="s">
-        <v>48</v>
-      </c>
-      <c r="U26" t="s">
-        <v>33</v>
-      </c>
-      <c r="X26">
+        <v>43</v>
+      </c>
+      <c r="P26" t="s">
+        <v>29</v>
+      </c>
+      <c r="W26" t="s">
+        <v>38</v>
+      </c>
+      <c r="X26" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB26">
         <v>2</v>
       </c>
     </row>
@@ -1531,7 +1636,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D27">
         <v>4</v>
@@ -1543,33 +1648,36 @@
         <v>30</v>
       </c>
       <c r="G27" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H27" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I27" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J27">
         <v>19</v>
       </c>
       <c r="K27" t="s">
-        <v>32</v>
-      </c>
-      <c r="R27" t="s">
-        <v>33</v>
-      </c>
-      <c r="S27" t="s">
-        <v>44</v>
-      </c>
-      <c r="T27" t="s">
-        <v>61</v>
-      </c>
-      <c r="U27" t="s">
-        <v>33</v>
-      </c>
-      <c r="X27">
+        <v>36</v>
+      </c>
+      <c r="P27" t="s">
+        <v>37</v>
+      </c>
+      <c r="W27" t="s">
+        <v>38</v>
+      </c>
+      <c r="X27" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB27">
         <v>2</v>
       </c>
     </row>
@@ -1581,7 +1689,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -1593,33 +1701,36 @@
         <v>11</v>
       </c>
       <c r="G28" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H28" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I28" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J28">
         <v>-5</v>
       </c>
       <c r="K28" t="s">
-        <v>38</v>
-      </c>
-      <c r="R28" t="s">
-        <v>26</v>
-      </c>
-      <c r="S28" t="s">
-        <v>52</v>
-      </c>
-      <c r="T28" t="s">
-        <v>47</v>
-      </c>
-      <c r="U28" t="s">
-        <v>33</v>
-      </c>
-      <c r="X28">
+        <v>43</v>
+      </c>
+      <c r="P28" t="s">
+        <v>72</v>
+      </c>
+      <c r="W28" t="s">
+        <v>30</v>
+      </c>
+      <c r="X28" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB28">
         <v>2</v>
       </c>
     </row>
@@ -1631,7 +1742,7 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D29">
         <v>2</v>
@@ -1643,33 +1754,36 @@
         <v>16</v>
       </c>
       <c r="G29" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H29" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I29" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J29">
         <v>-3</v>
       </c>
       <c r="K29" t="s">
-        <v>38</v>
-      </c>
-      <c r="R29" t="s">
-        <v>26</v>
-      </c>
-      <c r="S29" t="s">
-        <v>49</v>
-      </c>
-      <c r="T29" t="s">
-        <v>62</v>
-      </c>
-      <c r="U29" t="s">
-        <v>33</v>
-      </c>
-      <c r="X29">
+        <v>43</v>
+      </c>
+      <c r="P29" t="s">
+        <v>37</v>
+      </c>
+      <c r="W29" t="s">
+        <v>30</v>
+      </c>
+      <c r="X29" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB29">
         <v>2</v>
       </c>
     </row>
@@ -1681,7 +1795,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D30">
         <v>3</v>
@@ -1693,33 +1807,36 @@
         <v>19</v>
       </c>
       <c r="G30" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H30" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I30" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="J30">
         <v>19</v>
       </c>
       <c r="K30" t="s">
-        <v>32</v>
-      </c>
-      <c r="R30" t="s">
-        <v>26</v>
-      </c>
-      <c r="S30" t="s">
-        <v>44</v>
-      </c>
-      <c r="T30" t="s">
-        <v>61</v>
-      </c>
-      <c r="U30" t="s">
-        <v>26</v>
-      </c>
-      <c r="X30">
+        <v>36</v>
+      </c>
+      <c r="P30" t="s">
+        <v>29</v>
+      </c>
+      <c r="W30" t="s">
+        <v>30</v>
+      </c>
+      <c r="X30" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB30">
         <v>2</v>
       </c>
     </row>
@@ -1731,21 +1848,21 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F31">
         <v>3</v>
       </c>
       <c r="G31" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H31" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="I31" t="s">
-        <v>65</v>
-      </c>
-      <c r="X31">
+        <v>76</v>
+      </c>
+      <c r="AB31">
         <v>2</v>
       </c>
     </row>
@@ -1757,19 +1874,19 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F32">
         <v>-40</v>
       </c>
       <c r="G32" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H32" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I32" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33">
@@ -1780,7 +1897,7 @@
         <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -1792,18 +1909,18 @@
         <v>-45</v>
       </c>
       <c r="G33" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I33" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="J33">
         <v>7</v>
       </c>
       <c r="K33" t="s">
-        <v>38</v>
-      </c>
-      <c r="X33">
+        <v>43</v>
+      </c>
+      <c r="AB33">
         <v>3</v>
       </c>
     </row>
@@ -1815,7 +1932,7 @@
         <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D34">
         <v>2</v>
@@ -1827,30 +1944,33 @@
         <v>48</v>
       </c>
       <c r="G34" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H34" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I34" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J34">
         <v>-2</v>
       </c>
       <c r="K34" t="s">
-        <v>32</v>
-      </c>
-      <c r="R34" t="s">
-        <v>33</v>
-      </c>
-      <c r="S34" t="s">
-        <v>67</v>
-      </c>
-      <c r="U34" t="s">
-        <v>26</v>
-      </c>
-      <c r="X34">
+        <v>36</v>
+      </c>
+      <c r="P34" t="s">
+        <v>37</v>
+      </c>
+      <c r="W34" t="s">
+        <v>38</v>
+      </c>
+      <c r="X34" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB34">
         <v>3</v>
       </c>
     </row>
@@ -1862,7 +1982,7 @@
         <v>2</v>
       </c>
       <c r="C35" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D35">
         <v>3</v>
@@ -1874,30 +1994,33 @@
         <v>50</v>
       </c>
       <c r="G35" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H35" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I35" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J35">
         <v>14</v>
       </c>
       <c r="K35" t="s">
-        <v>38</v>
-      </c>
-      <c r="R35" t="s">
-        <v>33</v>
-      </c>
-      <c r="S35" t="s">
-        <v>34</v>
-      </c>
-      <c r="U35" t="s">
-        <v>33</v>
-      </c>
-      <c r="X35">
+        <v>43</v>
+      </c>
+      <c r="P35" t="s">
+        <v>29</v>
+      </c>
+      <c r="W35" t="s">
+        <v>38</v>
+      </c>
+      <c r="X35" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB35">
         <v>3</v>
       </c>
     </row>
@@ -1909,7 +2032,7 @@
         <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -1921,30 +2044,33 @@
         <v>36</v>
       </c>
       <c r="G36" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H36" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I36" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J36">
         <v>-2</v>
       </c>
       <c r="K36" t="s">
-        <v>32</v>
-      </c>
-      <c r="R36" t="s">
-        <v>26</v>
-      </c>
-      <c r="S36" t="s">
-        <v>68</v>
-      </c>
-      <c r="U36" t="s">
-        <v>33</v>
-      </c>
-      <c r="X36">
+        <v>36</v>
+      </c>
+      <c r="P36" t="s">
+        <v>79</v>
+      </c>
+      <c r="W36" t="s">
+        <v>30</v>
+      </c>
+      <c r="X36" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB36">
         <v>3</v>
       </c>
     </row>
@@ -1956,7 +2082,7 @@
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D37">
         <v>2</v>
@@ -1968,30 +2094,33 @@
         <v>38</v>
       </c>
       <c r="G37" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H37" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I37" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="J37">
         <v>-1</v>
       </c>
       <c r="K37" t="s">
-        <v>32</v>
-      </c>
-      <c r="R37" t="s">
-        <v>43</v>
-      </c>
-      <c r="S37" t="s">
-        <v>44</v>
-      </c>
-      <c r="U37" t="s">
-        <v>26</v>
-      </c>
-      <c r="X37">
+        <v>36</v>
+      </c>
+      <c r="P37" t="s">
+        <v>49</v>
+      </c>
+      <c r="W37" t="s">
+        <v>50</v>
+      </c>
+      <c r="X37" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB37">
         <v>3</v>
       </c>
     </row>
@@ -2003,7 +2132,7 @@
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -2015,36 +2144,39 @@
         <v>-39</v>
       </c>
       <c r="G38" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H38" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I38" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J38">
         <v>7</v>
       </c>
       <c r="K38" t="s">
-        <v>32</v>
-      </c>
-      <c r="R38" t="s">
-        <v>26</v>
-      </c>
-      <c r="S38" t="s">
-        <v>34</v>
-      </c>
-      <c r="T38" t="s">
-        <v>70</v>
-      </c>
-      <c r="U38" t="s">
-        <v>26</v>
-      </c>
-      <c r="V38" t="s">
-        <v>26</v>
-      </c>
-      <c r="X38">
+        <v>36</v>
+      </c>
+      <c r="P38" t="s">
+        <v>29</v>
+      </c>
+      <c r="W38" t="s">
+        <v>30</v>
+      </c>
+      <c r="X38" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB38">
         <v>3</v>
       </c>
     </row>
@@ -2056,7 +2188,7 @@
         <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D39">
         <v>2</v>
@@ -2068,36 +2200,39 @@
         <v>-46</v>
       </c>
       <c r="G39" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H39" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I39" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J39">
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>38</v>
-      </c>
-      <c r="R39" t="s">
-        <v>26</v>
-      </c>
-      <c r="S39" t="s">
-        <v>58</v>
-      </c>
-      <c r="T39" t="s">
-        <v>71</v>
-      </c>
-      <c r="U39" t="s">
-        <v>33</v>
-      </c>
-      <c r="V39" t="s">
-        <v>33</v>
-      </c>
-      <c r="X39">
+        <v>43</v>
+      </c>
+      <c r="P39" t="s">
+        <v>29</v>
+      </c>
+      <c r="W39" t="s">
+        <v>30</v>
+      </c>
+      <c r="X39" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA39" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB39">
         <v>3</v>
       </c>
     </row>
@@ -2109,7 +2244,7 @@
         <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D40">
         <v>3</v>
@@ -2121,33 +2256,36 @@
         <v>-46</v>
       </c>
       <c r="G40" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H40" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I40" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J40">
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>38</v>
-      </c>
-      <c r="R40" t="s">
-        <v>33</v>
-      </c>
-      <c r="S40" t="s">
-        <v>49</v>
-      </c>
-      <c r="T40" t="s">
-        <v>72</v>
-      </c>
-      <c r="U40" t="s">
-        <v>26</v>
-      </c>
-      <c r="X40">
+        <v>43</v>
+      </c>
+      <c r="P40" t="s">
+        <v>37</v>
+      </c>
+      <c r="W40" t="s">
+        <v>38</v>
+      </c>
+      <c r="X40" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB40">
         <v>3</v>
       </c>
     </row>
@@ -2159,7 +2297,7 @@
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D41">
         <v>4</v>
@@ -2171,15 +2309,15 @@
         <v>-47</v>
       </c>
       <c r="G41" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H41" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="I41" t="s">
-        <v>28</v>
-      </c>
-      <c r="X41">
+        <v>32</v>
+      </c>
+      <c r="AB41">
         <v>3</v>
       </c>
     </row>
@@ -2191,7 +2329,7 @@
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -2203,33 +2341,36 @@
         <v>-29</v>
       </c>
       <c r="G42" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H42" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I42" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J42">
         <v>8</v>
       </c>
       <c r="K42" t="s">
-        <v>38</v>
-      </c>
-      <c r="R42" t="s">
-        <v>26</v>
-      </c>
-      <c r="S42" t="s">
-        <v>35</v>
-      </c>
-      <c r="U42" t="s">
-        <v>26</v>
-      </c>
-      <c r="V42" t="s">
-        <v>33</v>
-      </c>
-      <c r="X42">
+        <v>43</v>
+      </c>
+      <c r="P42" t="s">
+        <v>29</v>
+      </c>
+      <c r="W42" t="s">
+        <v>30</v>
+      </c>
+      <c r="X42" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA42" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB42">
         <v>4</v>
       </c>
     </row>
@@ -2241,7 +2382,7 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D43">
         <v>2</v>
@@ -2253,30 +2394,33 @@
         <v>-37</v>
       </c>
       <c r="G43" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H43" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I43" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J43">
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>32</v>
-      </c>
-      <c r="R43" t="s">
-        <v>43</v>
-      </c>
-      <c r="S43" t="s">
-        <v>44</v>
-      </c>
-      <c r="U43" t="s">
-        <v>26</v>
-      </c>
-      <c r="X43">
+        <v>36</v>
+      </c>
+      <c r="P43" t="s">
+        <v>49</v>
+      </c>
+      <c r="W43" t="s">
+        <v>50</v>
+      </c>
+      <c r="X43" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB43">
         <v>4</v>
       </c>
     </row>
@@ -2288,7 +2432,7 @@
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D44">
         <v>3</v>
@@ -2300,30 +2444,33 @@
         <v>-37</v>
       </c>
       <c r="G44" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H44" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I44" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J44">
         <v>15</v>
       </c>
       <c r="K44" t="s">
-        <v>38</v>
-      </c>
-      <c r="R44" t="s">
         <v>43</v>
       </c>
-      <c r="S44" t="s">
-        <v>44</v>
-      </c>
-      <c r="U44" t="s">
-        <v>26</v>
-      </c>
-      <c r="X44">
+      <c r="P44" t="s">
+        <v>49</v>
+      </c>
+      <c r="W44" t="s">
+        <v>50</v>
+      </c>
+      <c r="X44" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB44">
         <v>4</v>
       </c>
     </row>
@@ -2335,7 +2482,7 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -2347,30 +2494,33 @@
         <v>48</v>
       </c>
       <c r="G45" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H45" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I45" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J45">
         <v>3</v>
       </c>
       <c r="K45" t="s">
-        <v>32</v>
-      </c>
-      <c r="R45" t="s">
-        <v>33</v>
-      </c>
-      <c r="S45" t="s">
-        <v>35</v>
-      </c>
-      <c r="U45" t="s">
-        <v>26</v>
-      </c>
-      <c r="X45">
+        <v>36</v>
+      </c>
+      <c r="P45" t="s">
+        <v>29</v>
+      </c>
+      <c r="W45" t="s">
+        <v>38</v>
+      </c>
+      <c r="X45" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB45">
         <v>4</v>
       </c>
     </row>
@@ -2382,7 +2532,7 @@
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D46">
         <v>2</v>
@@ -2394,30 +2544,33 @@
         <v>45</v>
       </c>
       <c r="G46" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H46" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I46" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="J46">
         <v>-11</v>
       </c>
       <c r="K46" t="s">
-        <v>32</v>
-      </c>
-      <c r="R46" t="s">
-        <v>33</v>
-      </c>
-      <c r="S46" t="s">
-        <v>58</v>
-      </c>
-      <c r="U46" t="s">
-        <v>26</v>
-      </c>
-      <c r="X46">
+        <v>36</v>
+      </c>
+      <c r="P46" t="s">
+        <v>29</v>
+      </c>
+      <c r="W46" t="s">
+        <v>38</v>
+      </c>
+      <c r="X46" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB46">
         <v>4</v>
       </c>
     </row>
@@ -2429,7 +2582,7 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D47">
         <v>3</v>
@@ -2441,30 +2594,33 @@
         <v>-44</v>
       </c>
       <c r="G47" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H47" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I47" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J47">
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>32</v>
-      </c>
-      <c r="R47" t="s">
-        <v>43</v>
-      </c>
-      <c r="S47" t="s">
-        <v>44</v>
-      </c>
-      <c r="U47" t="s">
-        <v>33</v>
-      </c>
-      <c r="X47">
+        <v>36</v>
+      </c>
+      <c r="P47" t="s">
+        <v>49</v>
+      </c>
+      <c r="W47" t="s">
+        <v>50</v>
+      </c>
+      <c r="X47" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB47">
         <v>4</v>
       </c>
     </row>
@@ -2476,7 +2632,7 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D48">
         <v>4</v>
@@ -2488,15 +2644,15 @@
         <v>-45</v>
       </c>
       <c r="G48" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H48" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="I48" t="s">
-        <v>28</v>
-      </c>
-      <c r="X48">
+        <v>32</v>
+      </c>
+      <c r="AB48">
         <v>4</v>
       </c>
     </row>
@@ -2508,7 +2664,7 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -2520,33 +2676,36 @@
         <v>-9</v>
       </c>
       <c r="G49" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H49" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I49" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J49">
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>38</v>
-      </c>
-      <c r="R49" t="s">
-        <v>26</v>
-      </c>
-      <c r="S49" t="s">
-        <v>49</v>
-      </c>
-      <c r="T49" t="s">
-        <v>47</v>
-      </c>
-      <c r="U49" t="s">
-        <v>26</v>
-      </c>
-      <c r="X49">
+        <v>43</v>
+      </c>
+      <c r="P49" t="s">
+        <v>72</v>
+      </c>
+      <c r="W49" t="s">
+        <v>30</v>
+      </c>
+      <c r="X49" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB49">
         <v>4</v>
       </c>
     </row>
@@ -2558,7 +2717,7 @@
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D50">
         <v>3</v>
@@ -2570,33 +2729,36 @@
         <v>-9</v>
       </c>
       <c r="G50" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H50" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I50" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="J50">
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>38</v>
-      </c>
-      <c r="R50" t="s">
-        <v>33</v>
-      </c>
-      <c r="S50" t="s">
-        <v>44</v>
-      </c>
-      <c r="T50" t="s">
-        <v>71</v>
-      </c>
-      <c r="U50" t="s">
-        <v>33</v>
-      </c>
-      <c r="X50">
+        <v>43</v>
+      </c>
+      <c r="P50" t="s">
+        <v>37</v>
+      </c>
+      <c r="W50" t="s">
+        <v>38</v>
+      </c>
+      <c r="X50" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB50">
         <v>4</v>
       </c>
     </row>
@@ -2608,7 +2770,7 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D51">
         <v>3</v>
@@ -2620,33 +2782,36 @@
         <v>-9</v>
       </c>
       <c r="G51" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H51" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I51" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J51">
         <v>16</v>
       </c>
       <c r="K51" t="s">
-        <v>32</v>
-      </c>
-      <c r="R51" t="s">
-        <v>26</v>
-      </c>
-      <c r="S51" t="s">
-        <v>35</v>
-      </c>
-      <c r="T51" t="s">
-        <v>75</v>
-      </c>
-      <c r="U51" t="s">
-        <v>33</v>
-      </c>
-      <c r="X51">
+        <v>36</v>
+      </c>
+      <c r="P51" t="s">
+        <v>72</v>
+      </c>
+      <c r="W51" t="s">
+        <v>30</v>
+      </c>
+      <c r="X51" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB51">
         <v>4</v>
       </c>
     </row>
@@ -2658,7 +2823,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -2670,33 +2835,36 @@
         <v>-25</v>
       </c>
       <c r="G52" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H52" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I52" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J52">
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>38</v>
-      </c>
-      <c r="R52" t="s">
-        <v>33</v>
-      </c>
-      <c r="S52" t="s">
-        <v>44</v>
-      </c>
-      <c r="T52" t="s">
-        <v>76</v>
-      </c>
-      <c r="U52" t="s">
-        <v>26</v>
-      </c>
-      <c r="X52">
+        <v>43</v>
+      </c>
+      <c r="P52" t="s">
+        <v>37</v>
+      </c>
+      <c r="W52" t="s">
+        <v>38</v>
+      </c>
+      <c r="X52" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB52">
         <v>4</v>
       </c>
     </row>
@@ -2708,7 +2876,7 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D53">
         <v>2</v>
@@ -2720,36 +2888,39 @@
         <v>-25</v>
       </c>
       <c r="G53" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H53" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I53" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J53">
         <v>-4</v>
       </c>
       <c r="K53" t="s">
-        <v>38</v>
-      </c>
-      <c r="R53" t="s">
-        <v>26</v>
-      </c>
-      <c r="S53" t="s">
-        <v>34</v>
-      </c>
-      <c r="T53" t="s">
-        <v>70</v>
-      </c>
-      <c r="U53" t="s">
-        <v>33</v>
-      </c>
-      <c r="V53" t="s">
-        <v>26</v>
-      </c>
-      <c r="X53">
+        <v>43</v>
+      </c>
+      <c r="P53" t="s">
+        <v>37</v>
+      </c>
+      <c r="W53" t="s">
+        <v>30</v>
+      </c>
+      <c r="X53" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA53" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB53">
         <v>4</v>
       </c>
     </row>
@@ -2761,7 +2932,7 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D54">
         <v>3</v>
@@ -2773,33 +2944,36 @@
         <v>-21</v>
       </c>
       <c r="G54" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H54" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I54" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J54">
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>38</v>
-      </c>
-      <c r="R54" t="s">
-        <v>26</v>
-      </c>
-      <c r="S54" t="s">
-        <v>44</v>
-      </c>
-      <c r="T54" t="s">
-        <v>71</v>
-      </c>
-      <c r="U54" t="s">
-        <v>26</v>
-      </c>
-      <c r="X54">
+        <v>43</v>
+      </c>
+      <c r="P54" t="s">
+        <v>29</v>
+      </c>
+      <c r="W54" t="s">
+        <v>30</v>
+      </c>
+      <c r="X54" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB54">
         <v>4</v>
       </c>
     </row>
@@ -2811,7 +2985,7 @@
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D55">
         <v>4</v>
@@ -2823,15 +2997,15 @@
         <v>-21</v>
       </c>
       <c r="G55" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H55" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="I55" t="s">
-        <v>28</v>
-      </c>
-      <c r="X55">
+        <v>32</v>
+      </c>
+      <c r="AB55">
         <v>4</v>
       </c>
     </row>
@@ -2843,7 +3017,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -2855,30 +3029,33 @@
         <v>-42</v>
       </c>
       <c r="G56" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H56" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I56" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J56">
         <v>2</v>
       </c>
       <c r="K56" t="s">
-        <v>32</v>
-      </c>
-      <c r="R56" t="s">
-        <v>26</v>
-      </c>
-      <c r="S56" t="s">
-        <v>35</v>
-      </c>
-      <c r="U56" t="s">
-        <v>33</v>
-      </c>
-      <c r="X56">
+        <v>36</v>
+      </c>
+      <c r="P56" t="s">
+        <v>29</v>
+      </c>
+      <c r="W56" t="s">
+        <v>30</v>
+      </c>
+      <c r="X56" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB56">
         <v>5</v>
       </c>
     </row>
@@ -2890,7 +3067,7 @@
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -2902,33 +3079,33 @@
         <v>-44</v>
       </c>
       <c r="G57" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H57" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I57" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J57">
         <v>-1</v>
       </c>
       <c r="K57" t="s">
-        <v>32</v>
-      </c>
-      <c r="R57" t="s">
-        <v>26</v>
-      </c>
-      <c r="S57" t="s">
-        <v>68</v>
-      </c>
-      <c r="U57" t="s">
-        <v>26</v>
-      </c>
-      <c r="V57" t="s">
-        <v>33</v>
-      </c>
-      <c r="X57">
+        <v>36</v>
+      </c>
+      <c r="W57" t="s">
+        <v>30</v>
+      </c>
+      <c r="X57" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA57" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB57">
         <v>5</v>
       </c>
     </row>
@@ -2940,7 +3117,7 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D58">
         <v>3</v>
@@ -2952,30 +3129,33 @@
         <v>-43</v>
       </c>
       <c r="G58" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H58" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I58" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J58">
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>32</v>
-      </c>
-      <c r="R58" t="s">
-        <v>43</v>
-      </c>
-      <c r="S58" t="s">
-        <v>44</v>
-      </c>
-      <c r="U58" t="s">
-        <v>33</v>
-      </c>
-      <c r="X58">
+        <v>36</v>
+      </c>
+      <c r="P58" t="s">
+        <v>49</v>
+      </c>
+      <c r="W58" t="s">
+        <v>50</v>
+      </c>
+      <c r="X58" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB58">
         <v>5</v>
       </c>
     </row>
@@ -2987,7 +3167,7 @@
         <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D59">
         <v>4</v>
@@ -2999,15 +3179,15 @@
         <v>-43</v>
       </c>
       <c r="G59" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H59" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="I59" t="s">
-        <v>28</v>
-      </c>
-      <c r="X59">
+        <v>32</v>
+      </c>
+      <c r="AB59">
         <v>5</v>
       </c>
     </row>
@@ -3019,7 +3199,7 @@
         <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -3031,33 +3211,36 @@
         <v>-24</v>
       </c>
       <c r="G60" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H60" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I60" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J60">
         <v>12</v>
       </c>
       <c r="K60" t="s">
-        <v>32</v>
-      </c>
-      <c r="R60" t="s">
-        <v>26</v>
-      </c>
-      <c r="S60" t="s">
-        <v>58</v>
-      </c>
-      <c r="T60" t="s">
-        <v>77</v>
-      </c>
-      <c r="U60" t="s">
-        <v>33</v>
-      </c>
-      <c r="X60">
+        <v>36</v>
+      </c>
+      <c r="P60" t="s">
+        <v>37</v>
+      </c>
+      <c r="W60" t="s">
+        <v>30</v>
+      </c>
+      <c r="X60" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB60">
         <v>5</v>
       </c>
     </row>
@@ -3069,7 +3252,7 @@
         <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -3081,33 +3264,36 @@
         <v>-36</v>
       </c>
       <c r="G61" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H61" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I61" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J61">
         <v>5</v>
       </c>
       <c r="K61" t="s">
-        <v>32</v>
-      </c>
-      <c r="R61" t="s">
-        <v>26</v>
-      </c>
-      <c r="S61" t="s">
-        <v>35</v>
-      </c>
-      <c r="T61" t="s">
-        <v>78</v>
-      </c>
-      <c r="U61" t="s">
-        <v>26</v>
-      </c>
-      <c r="X61">
+        <v>36</v>
+      </c>
+      <c r="P61" t="s">
+        <v>29</v>
+      </c>
+      <c r="W61" t="s">
+        <v>30</v>
+      </c>
+      <c r="X61" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB61">
         <v>5</v>
       </c>
     </row>
@@ -3119,7 +3305,7 @@
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D62">
         <v>2</v>
@@ -3131,33 +3317,36 @@
         <v>-41</v>
       </c>
       <c r="G62" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H62" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I62" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J62">
         <v>8</v>
       </c>
       <c r="K62" t="s">
-        <v>32</v>
-      </c>
-      <c r="R62" t="s">
-        <v>33</v>
-      </c>
-      <c r="S62" t="s">
-        <v>44</v>
-      </c>
-      <c r="T62" t="s">
-        <v>71</v>
-      </c>
-      <c r="U62" t="s">
-        <v>33</v>
-      </c>
-      <c r="X62">
+        <v>36</v>
+      </c>
+      <c r="P62" t="s">
+        <v>37</v>
+      </c>
+      <c r="W62" t="s">
+        <v>38</v>
+      </c>
+      <c r="X62" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB62">
         <v>5</v>
       </c>
     </row>
@@ -3169,7 +3358,7 @@
         <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -3181,33 +3370,36 @@
         <v>-49</v>
       </c>
       <c r="G63" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H63" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I63" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J63">
         <v>-5</v>
       </c>
       <c r="K63" t="s">
-        <v>38</v>
-      </c>
-      <c r="R63" t="s">
-        <v>26</v>
-      </c>
-      <c r="S63" t="s">
-        <v>44</v>
-      </c>
-      <c r="T63" t="s">
-        <v>71</v>
-      </c>
-      <c r="U63" t="s">
-        <v>26</v>
-      </c>
-      <c r="X63">
+        <v>43</v>
+      </c>
+      <c r="P63" t="s">
+        <v>29</v>
+      </c>
+      <c r="W63" t="s">
+        <v>30</v>
+      </c>
+      <c r="X63" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB63">
         <v>5</v>
       </c>
     </row>
@@ -3219,7 +3411,7 @@
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -3231,33 +3423,36 @@
         <v>-44</v>
       </c>
       <c r="G64" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H64" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I64" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J64">
         <v>-5</v>
       </c>
       <c r="K64" t="s">
-        <v>38</v>
-      </c>
-      <c r="R64" t="s">
-        <v>26</v>
-      </c>
-      <c r="S64" t="s">
-        <v>58</v>
-      </c>
-      <c r="T64" t="s">
-        <v>54</v>
-      </c>
-      <c r="U64" t="s">
-        <v>26</v>
-      </c>
-      <c r="X64">
+        <v>43</v>
+      </c>
+      <c r="P64" t="s">
+        <v>37</v>
+      </c>
+      <c r="W64" t="s">
+        <v>30</v>
+      </c>
+      <c r="X64" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB64">
         <v>5</v>
       </c>
     </row>
@@ -3269,7 +3464,7 @@
         <v>2</v>
       </c>
       <c r="C65" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -3281,36 +3476,39 @@
         <v>-39</v>
       </c>
       <c r="G65" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H65" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I65" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J65">
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>38</v>
-      </c>
-      <c r="R65" t="s">
-        <v>33</v>
-      </c>
-      <c r="S65" t="s">
-        <v>58</v>
-      </c>
-      <c r="T65" t="s">
-        <v>76</v>
-      </c>
-      <c r="U65" t="s">
-        <v>26</v>
-      </c>
-      <c r="V65" t="s">
-        <v>26</v>
-      </c>
-      <c r="X65">
+        <v>43</v>
+      </c>
+      <c r="P65" t="s">
+        <v>29</v>
+      </c>
+      <c r="W65" t="s">
+        <v>38</v>
+      </c>
+      <c r="X65" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA65" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB65">
         <v>5</v>
       </c>
     </row>
@@ -3322,7 +3520,7 @@
         <v>2</v>
       </c>
       <c r="C66" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D66">
         <v>2</v>
@@ -3334,33 +3532,36 @@
         <v>-39</v>
       </c>
       <c r="G66" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H66" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I66" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J66">
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>38</v>
-      </c>
-      <c r="R66" t="s">
-        <v>33</v>
-      </c>
-      <c r="S66" t="s">
-        <v>58</v>
-      </c>
-      <c r="T66" t="s">
-        <v>79</v>
-      </c>
-      <c r="U66" t="s">
-        <v>33</v>
-      </c>
-      <c r="X66">
+        <v>43</v>
+      </c>
+      <c r="P66" t="s">
+        <v>29</v>
+      </c>
+      <c r="W66" t="s">
+        <v>38</v>
+      </c>
+      <c r="X66" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB66">
         <v>5</v>
       </c>
     </row>
@@ -3372,7 +3573,7 @@
         <v>2</v>
       </c>
       <c r="C67" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D67">
         <v>3</v>
@@ -3384,33 +3585,36 @@
         <v>-39</v>
       </c>
       <c r="G67" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H67" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I67" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J67">
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>38</v>
-      </c>
-      <c r="R67" t="s">
-        <v>33</v>
-      </c>
-      <c r="S67" t="s">
-        <v>44</v>
-      </c>
-      <c r="T67" t="s">
-        <v>71</v>
-      </c>
-      <c r="U67" t="s">
-        <v>33</v>
-      </c>
-      <c r="X67">
+        <v>43</v>
+      </c>
+      <c r="P67" t="s">
+        <v>29</v>
+      </c>
+      <c r="W67" t="s">
+        <v>38</v>
+      </c>
+      <c r="X67" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB67">
         <v>5</v>
       </c>
     </row>
@@ -3422,7 +3626,7 @@
         <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D68">
         <v>4</v>
@@ -3434,15 +3638,15 @@
         <v>-39</v>
       </c>
       <c r="G68" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H68" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="I68" t="s">
-        <v>80</v>
-      </c>
-      <c r="X68">
+        <v>92</v>
+      </c>
+      <c r="AB68">
         <v>5</v>
       </c>
     </row>
@@ -3454,7 +3658,7 @@
         <v>2</v>
       </c>
       <c r="C69" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -3466,30 +3670,33 @@
         <v>-28</v>
       </c>
       <c r="G69" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H69" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I69" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J69">
         <v>5</v>
       </c>
       <c r="K69" t="s">
-        <v>38</v>
-      </c>
-      <c r="R69" t="s">
         <v>43</v>
       </c>
-      <c r="S69" t="s">
-        <v>44</v>
-      </c>
-      <c r="U69" t="s">
-        <v>33</v>
-      </c>
-      <c r="X69">
+      <c r="P69" t="s">
+        <v>49</v>
+      </c>
+      <c r="W69" t="s">
+        <v>50</v>
+      </c>
+      <c r="X69" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB69">
         <v>6</v>
       </c>
     </row>
@@ -3501,7 +3708,7 @@
         <v>3</v>
       </c>
       <c r="C70" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D70">
         <v>2</v>
@@ -3513,15 +3720,15 @@
         <v>-40</v>
       </c>
       <c r="G70" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H70" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I70" t="s">
-        <v>82</v>
-      </c>
-      <c r="X70">
+        <v>94</v>
+      </c>
+      <c r="AB70">
         <v>6</v>
       </c>
     </row>
@@ -3533,7 +3740,7 @@
         <v>3</v>
       </c>
       <c r="C71" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -3545,33 +3752,36 @@
         <v>-21</v>
       </c>
       <c r="G71" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H71" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I71" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J71">
         <v>7</v>
       </c>
       <c r="K71" t="s">
-        <v>32</v>
-      </c>
-      <c r="R71" t="s">
-        <v>26</v>
-      </c>
-      <c r="S71" t="s">
-        <v>49</v>
-      </c>
-      <c r="T71" t="s">
-        <v>47</v>
-      </c>
-      <c r="U71" t="s">
-        <v>26</v>
-      </c>
-      <c r="X71">
+        <v>36</v>
+      </c>
+      <c r="P71" t="s">
+        <v>72</v>
+      </c>
+      <c r="W71" t="s">
+        <v>30</v>
+      </c>
+      <c r="X71" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB71">
         <v>5</v>
       </c>
     </row>
@@ -3583,7 +3793,7 @@
         <v>3</v>
       </c>
       <c r="C72" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D72">
         <v>2</v>
@@ -3595,33 +3805,36 @@
         <v>-28</v>
       </c>
       <c r="G72" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H72" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I72" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J72">
         <v>5</v>
       </c>
       <c r="K72" t="s">
-        <v>32</v>
-      </c>
-      <c r="R72" t="s">
-        <v>26</v>
-      </c>
-      <c r="S72" t="s">
-        <v>49</v>
-      </c>
-      <c r="T72" t="s">
-        <v>47</v>
-      </c>
-      <c r="U72" t="s">
-        <v>26</v>
-      </c>
-      <c r="X72">
+        <v>36</v>
+      </c>
+      <c r="P72" t="s">
+        <v>72</v>
+      </c>
+      <c r="W72" t="s">
+        <v>30</v>
+      </c>
+      <c r="X72" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB72">
         <v>5</v>
       </c>
     </row>
@@ -3633,7 +3846,7 @@
         <v>3</v>
       </c>
       <c r="C73" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -3645,33 +3858,36 @@
         <v>-33</v>
       </c>
       <c r="G73" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H73" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I73" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J73">
         <v>-1</v>
       </c>
       <c r="K73" t="s">
-        <v>38</v>
-      </c>
-      <c r="R73" t="s">
-        <v>33</v>
-      </c>
-      <c r="S73" t="s">
-        <v>49</v>
-      </c>
-      <c r="T73" t="s">
-        <v>60</v>
-      </c>
-      <c r="U73" t="s">
-        <v>26</v>
-      </c>
-      <c r="X73">
+        <v>43</v>
+      </c>
+      <c r="P73" t="s">
+        <v>72</v>
+      </c>
+      <c r="W73" t="s">
+        <v>38</v>
+      </c>
+      <c r="X73" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB73">
         <v>5</v>
       </c>
     </row>
@@ -3683,7 +3899,7 @@
         <v>3</v>
       </c>
       <c r="C74" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D74">
         <v>2</v>
@@ -3695,36 +3911,39 @@
         <v>-32</v>
       </c>
       <c r="G74" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H74" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I74" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J74">
         <v>4</v>
       </c>
       <c r="K74" t="s">
-        <v>38</v>
-      </c>
-      <c r="R74" t="s">
-        <v>33</v>
-      </c>
-      <c r="S74" t="s">
-        <v>58</v>
-      </c>
-      <c r="T74" t="s">
-        <v>76</v>
-      </c>
-      <c r="U74" t="s">
-        <v>33</v>
-      </c>
-      <c r="V74" t="s">
-        <v>26</v>
-      </c>
-      <c r="X74">
+        <v>43</v>
+      </c>
+      <c r="P74" t="s">
+        <v>29</v>
+      </c>
+      <c r="W74" t="s">
+        <v>38</v>
+      </c>
+      <c r="X74" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA74" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB74">
         <v>5</v>
       </c>
     </row>
@@ -3736,7 +3955,7 @@
         <v>3</v>
       </c>
       <c r="C75" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D75">
         <v>3</v>
@@ -3748,33 +3967,36 @@
         <v>-36</v>
       </c>
       <c r="G75" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H75" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I75" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J75">
         <v>43</v>
       </c>
       <c r="K75" t="s">
-        <v>32</v>
-      </c>
-      <c r="R75" t="s">
-        <v>26</v>
-      </c>
-      <c r="S75" t="s">
-        <v>58</v>
-      </c>
-      <c r="T75" t="s">
-        <v>61</v>
-      </c>
-      <c r="U75" t="s">
-        <v>26</v>
-      </c>
-      <c r="X75">
+        <v>36</v>
+      </c>
+      <c r="P75" t="s">
+        <v>37</v>
+      </c>
+      <c r="W75" t="s">
+        <v>30</v>
+      </c>
+      <c r="X75" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB75">
         <v>5</v>
       </c>
     </row>
@@ -3786,7 +4008,7 @@
         <v>3</v>
       </c>
       <c r="C76" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -3798,33 +4020,36 @@
         <v>21</v>
       </c>
       <c r="G76" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H76" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I76" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J76">
         <v>-1</v>
       </c>
       <c r="K76" t="s">
-        <v>38</v>
-      </c>
-      <c r="R76" t="s">
-        <v>26</v>
-      </c>
-      <c r="S76" t="s">
-        <v>49</v>
-      </c>
-      <c r="T76" t="s">
-        <v>47</v>
-      </c>
-      <c r="U76" t="s">
-        <v>26</v>
-      </c>
-      <c r="X76">
+        <v>43</v>
+      </c>
+      <c r="P76" t="s">
+        <v>72</v>
+      </c>
+      <c r="W76" t="s">
+        <v>30</v>
+      </c>
+      <c r="X76" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB76">
         <v>5</v>
       </c>
     </row>
@@ -3836,7 +4061,7 @@
         <v>3</v>
       </c>
       <c r="C77" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D77">
         <v>2</v>
@@ -3848,33 +4073,36 @@
         <v>22</v>
       </c>
       <c r="G77" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H77" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I77" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J77">
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>38</v>
-      </c>
-      <c r="R77" t="s">
-        <v>26</v>
-      </c>
-      <c r="S77" t="s">
-        <v>44</v>
-      </c>
-      <c r="T77" t="s">
-        <v>76</v>
-      </c>
-      <c r="U77" t="s">
-        <v>26</v>
-      </c>
-      <c r="X77">
+        <v>43</v>
+      </c>
+      <c r="P77" t="s">
+        <v>29</v>
+      </c>
+      <c r="W77" t="s">
+        <v>30</v>
+      </c>
+      <c r="X77" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB77">
         <v>5</v>
       </c>
     </row>
@@ -3886,7 +4114,7 @@
         <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D78">
         <v>3</v>
@@ -3898,33 +4126,36 @@
         <v>22</v>
       </c>
       <c r="G78" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H78" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I78" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J78">
         <v>-3</v>
       </c>
       <c r="K78" t="s">
-        <v>38</v>
-      </c>
-      <c r="R78" t="s">
-        <v>26</v>
-      </c>
-      <c r="S78" t="s">
-        <v>58</v>
-      </c>
-      <c r="T78" t="s">
-        <v>60</v>
-      </c>
-      <c r="U78" t="s">
-        <v>26</v>
-      </c>
-      <c r="X78">
+        <v>43</v>
+      </c>
+      <c r="P78" t="s">
+        <v>29</v>
+      </c>
+      <c r="W78" t="s">
+        <v>30</v>
+      </c>
+      <c r="X78" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB78">
         <v>5</v>
       </c>
     </row>
@@ -3936,7 +4167,7 @@
         <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D79">
         <v>4</v>
@@ -3948,15 +4179,15 @@
         <v>25</v>
       </c>
       <c r="G79" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H79" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I79" t="s">
-        <v>65</v>
-      </c>
-      <c r="X79">
+        <v>76</v>
+      </c>
+      <c r="AB79">
         <v>5</v>
       </c>
     </row>
@@ -3968,19 +4199,19 @@
         <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F80">
         <v>-40</v>
       </c>
       <c r="G80" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H80" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I80" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="81">
@@ -3991,7 +4222,7 @@
         <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -4003,30 +4234,33 @@
         <v>-36</v>
       </c>
       <c r="G81" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H81" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I81" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J81">
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>32</v>
-      </c>
-      <c r="R81" t="s">
-        <v>33</v>
-      </c>
-      <c r="S81" t="s">
-        <v>58</v>
-      </c>
-      <c r="U81" t="s">
-        <v>33</v>
-      </c>
-      <c r="X81">
+        <v>36</v>
+      </c>
+      <c r="P81" t="s">
+        <v>37</v>
+      </c>
+      <c r="W81" t="s">
+        <v>38</v>
+      </c>
+      <c r="X81" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB81">
         <v>7</v>
       </c>
     </row>
@@ -4038,7 +4272,7 @@
         <v>3</v>
       </c>
       <c r="C82" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D82">
         <v>2</v>
@@ -4050,30 +4284,33 @@
         <v>-36</v>
       </c>
       <c r="G82" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H82" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I82" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J82">
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>32</v>
-      </c>
-      <c r="R82" t="s">
-        <v>43</v>
-      </c>
-      <c r="S82" t="s">
-        <v>44</v>
-      </c>
-      <c r="U82" t="s">
-        <v>33</v>
-      </c>
-      <c r="X82">
+        <v>36</v>
+      </c>
+      <c r="P82" t="s">
+        <v>49</v>
+      </c>
+      <c r="W82" t="s">
+        <v>50</v>
+      </c>
+      <c r="X82" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB82">
         <v>7</v>
       </c>
     </row>
@@ -4085,7 +4322,7 @@
         <v>3</v>
       </c>
       <c r="C83" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D83">
         <v>3</v>
@@ -4097,33 +4334,36 @@
         <v>-36</v>
       </c>
       <c r="G83" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H83" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I83" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J83">
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>32</v>
-      </c>
-      <c r="R83" t="s">
-        <v>33</v>
-      </c>
-      <c r="S83" t="s">
-        <v>84</v>
-      </c>
-      <c r="U83" t="s">
-        <v>26</v>
-      </c>
-      <c r="V83" t="s">
-        <v>33</v>
-      </c>
-      <c r="X83">
+        <v>36</v>
+      </c>
+      <c r="P83" t="s">
+        <v>44</v>
+      </c>
+      <c r="W83" t="s">
+        <v>38</v>
+      </c>
+      <c r="X83" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA83" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB83">
         <v>7</v>
       </c>
     </row>
@@ -4135,7 +4375,7 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D84">
         <v>4</v>
@@ -4147,15 +4387,15 @@
         <v>-36</v>
       </c>
       <c r="G84" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H84" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="I84" t="s">
-        <v>28</v>
-      </c>
-      <c r="X84">
+        <v>32</v>
+      </c>
+      <c r="AB84">
         <v>7</v>
       </c>
     </row>
@@ -4167,7 +4407,7 @@
         <v>3</v>
       </c>
       <c r="C85" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -4179,33 +4419,36 @@
         <v>-35</v>
       </c>
       <c r="G85" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H85" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I85" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K85" t="s">
-        <v>38</v>
-      </c>
-      <c r="R85" t="s">
-        <v>26</v>
-      </c>
-      <c r="S85" t="s">
-        <v>44</v>
-      </c>
-      <c r="T85" t="s">
-        <v>71</v>
-      </c>
-      <c r="U85" t="s">
-        <v>26</v>
-      </c>
-      <c r="V85" t="s">
-        <v>26</v>
-      </c>
-      <c r="X85">
+        <v>43</v>
+      </c>
+      <c r="P85" t="s">
+        <v>72</v>
+      </c>
+      <c r="W85" t="s">
+        <v>30</v>
+      </c>
+      <c r="X85" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y85" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA85" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB85">
         <v>6</v>
       </c>
     </row>
@@ -4217,7 +4460,7 @@
         <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -4229,33 +4472,36 @@
         <v>41</v>
       </c>
       <c r="G86" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H86" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I86" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J86">
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>32</v>
-      </c>
-      <c r="R86" t="s">
-        <v>26</v>
-      </c>
-      <c r="S86" t="s">
-        <v>58</v>
-      </c>
-      <c r="U86" t="s">
-        <v>26</v>
-      </c>
-      <c r="V86" t="s">
-        <v>26</v>
-      </c>
-      <c r="X86">
+        <v>36</v>
+      </c>
+      <c r="P86" t="s">
+        <v>29</v>
+      </c>
+      <c r="W86" t="s">
+        <v>30</v>
+      </c>
+      <c r="X86" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA86" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB86">
         <v>8</v>
       </c>
     </row>
@@ -4267,7 +4513,7 @@
         <v>3</v>
       </c>
       <c r="C87" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D87">
         <v>2</v>
@@ -4279,33 +4525,36 @@
         <v>41</v>
       </c>
       <c r="G87" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H87" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I87" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J87">
         <v>6</v>
       </c>
       <c r="K87" t="s">
-        <v>38</v>
-      </c>
-      <c r="R87" t="s">
-        <v>26</v>
-      </c>
-      <c r="S87" t="s">
-        <v>39</v>
-      </c>
-      <c r="U87" t="s">
-        <v>26</v>
-      </c>
-      <c r="V87" t="s">
-        <v>33</v>
-      </c>
-      <c r="X87">
+        <v>43</v>
+      </c>
+      <c r="P87" t="s">
+        <v>44</v>
+      </c>
+      <c r="W87" t="s">
+        <v>30</v>
+      </c>
+      <c r="X87" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA87" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB87">
         <v>8</v>
       </c>
     </row>
@@ -4317,7 +4566,7 @@
         <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D88">
         <v>3</v>
@@ -4329,24 +4578,27 @@
         <v>35</v>
       </c>
       <c r="G88" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I88" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J88">
         <v>12</v>
       </c>
       <c r="K88" t="s">
-        <v>38</v>
-      </c>
-      <c r="R88" t="s">
-        <v>26</v>
-      </c>
-      <c r="S88" t="s">
-        <v>39</v>
-      </c>
-      <c r="X88">
+        <v>43</v>
+      </c>
+      <c r="P88" t="s">
+        <v>44</v>
+      </c>
+      <c r="W88" t="s">
+        <v>30</v>
+      </c>
+      <c r="X88" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB88">
         <v>8</v>
       </c>
     </row>
@@ -4358,7 +4610,7 @@
         <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -4370,30 +4622,33 @@
         <v>23</v>
       </c>
       <c r="G89" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H89" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I89" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J89">
         <v>2</v>
       </c>
       <c r="K89" t="s">
-        <v>32</v>
-      </c>
-      <c r="R89" t="s">
-        <v>33</v>
-      </c>
-      <c r="S89" t="s">
-        <v>86</v>
-      </c>
-      <c r="U89" t="s">
-        <v>26</v>
-      </c>
-      <c r="X89">
+        <v>36</v>
+      </c>
+      <c r="P89" t="s">
+        <v>37</v>
+      </c>
+      <c r="W89" t="s">
+        <v>38</v>
+      </c>
+      <c r="X89" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB89">
         <v>8</v>
       </c>
     </row>
@@ -4405,7 +4660,7 @@
         <v>3</v>
       </c>
       <c r="C90" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D90">
         <v>2</v>
@@ -4417,30 +4672,33 @@
         <v>21</v>
       </c>
       <c r="G90" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H90" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I90" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="J90">
         <v>21</v>
       </c>
       <c r="K90" t="s">
-        <v>38</v>
-      </c>
-      <c r="R90" t="s">
         <v>43</v>
       </c>
-      <c r="S90" t="s">
-        <v>44</v>
-      </c>
-      <c r="U90" t="s">
-        <v>33</v>
-      </c>
-      <c r="X90">
+      <c r="P90" t="s">
+        <v>49</v>
+      </c>
+      <c r="W90" t="s">
+        <v>50</v>
+      </c>
+      <c r="X90" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB90">
         <v>8</v>
       </c>
     </row>
@@ -4452,21 +4710,21 @@
         <v>3</v>
       </c>
       <c r="C91" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F91">
         <v>3</v>
       </c>
       <c r="G91" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H91" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="I91" t="s">
-        <v>65</v>
-      </c>
-      <c r="X91">
+        <v>76</v>
+      </c>
+      <c r="AB91">
         <v>8</v>
       </c>
     </row>
@@ -4478,19 +4736,19 @@
         <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F92">
         <v>-40</v>
       </c>
       <c r="G92" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H92" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I92" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="93">
@@ -4501,7 +4759,7 @@
         <v>3</v>
       </c>
       <c r="C93" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -4513,33 +4771,36 @@
         <v>-37</v>
       </c>
       <c r="G93" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H93" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I93" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J93">
         <v>9</v>
       </c>
       <c r="K93" t="s">
-        <v>32</v>
-      </c>
-      <c r="R93" t="s">
-        <v>33</v>
-      </c>
-      <c r="S93" t="s">
-        <v>44</v>
-      </c>
-      <c r="T93" t="s">
-        <v>71</v>
-      </c>
-      <c r="U93" t="s">
-        <v>33</v>
-      </c>
-      <c r="X93">
+        <v>36</v>
+      </c>
+      <c r="P93" t="s">
+        <v>72</v>
+      </c>
+      <c r="W93" t="s">
+        <v>38</v>
+      </c>
+      <c r="X93" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y93" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB93">
         <v>7</v>
       </c>
     </row>
@@ -4551,7 +4812,7 @@
         <v>3</v>
       </c>
       <c r="C94" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D94">
         <v>2</v>
@@ -4563,33 +4824,36 @@
         <v>-46</v>
       </c>
       <c r="G94" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H94" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I94" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J94">
         <v>-2</v>
       </c>
       <c r="K94" t="s">
-        <v>38</v>
-      </c>
-      <c r="R94" t="s">
-        <v>26</v>
-      </c>
-      <c r="S94" t="s">
-        <v>58</v>
-      </c>
-      <c r="T94" t="s">
-        <v>60</v>
-      </c>
-      <c r="U94" t="s">
-        <v>33</v>
-      </c>
-      <c r="X94">
+        <v>43</v>
+      </c>
+      <c r="P94" t="s">
+        <v>37</v>
+      </c>
+      <c r="W94" t="s">
+        <v>30</v>
+      </c>
+      <c r="X94" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y94" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB94">
         <v>7</v>
       </c>
     </row>
@@ -4601,7 +4865,7 @@
         <v>3</v>
       </c>
       <c r="C95" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D95">
         <v>3</v>
@@ -4613,33 +4877,36 @@
         <v>-44</v>
       </c>
       <c r="G95" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H95" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I95" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J95">
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>38</v>
-      </c>
-      <c r="R95" t="s">
-        <v>26</v>
-      </c>
-      <c r="S95" t="s">
-        <v>58</v>
-      </c>
-      <c r="T95" t="s">
-        <v>53</v>
-      </c>
-      <c r="U95" t="s">
-        <v>26</v>
-      </c>
-      <c r="X95">
+        <v>43</v>
+      </c>
+      <c r="P95" t="s">
+        <v>37</v>
+      </c>
+      <c r="W95" t="s">
+        <v>30</v>
+      </c>
+      <c r="X95" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y95" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB95">
         <v>7</v>
       </c>
     </row>
@@ -4651,7 +4918,7 @@
         <v>3</v>
       </c>
       <c r="C96" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D96">
         <v>4</v>
@@ -4663,15 +4930,15 @@
         <v>-44</v>
       </c>
       <c r="G96" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H96" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="I96" t="s">
-        <v>28</v>
-      </c>
-      <c r="X96">
+        <v>32</v>
+      </c>
+      <c r="AB96">
         <v>7</v>
       </c>
     </row>
@@ -4683,7 +4950,7 @@
         <v>3</v>
       </c>
       <c r="C97" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -4695,30 +4962,33 @@
         <v>-22</v>
       </c>
       <c r="G97" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H97" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I97" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J97">
         <v>18</v>
       </c>
       <c r="K97" t="s">
-        <v>38</v>
-      </c>
-      <c r="R97" t="s">
-        <v>26</v>
-      </c>
-      <c r="S97" t="s">
-        <v>35</v>
-      </c>
-      <c r="U97" t="s">
-        <v>33</v>
-      </c>
-      <c r="X97">
+        <v>43</v>
+      </c>
+      <c r="P97" t="s">
+        <v>37</v>
+      </c>
+      <c r="W97" t="s">
+        <v>30</v>
+      </c>
+      <c r="X97" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB97">
         <v>9</v>
       </c>
     </row>
@@ -4730,7 +5000,7 @@
         <v>3</v>
       </c>
       <c r="C98" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -4742,30 +5012,33 @@
         <v>-40</v>
       </c>
       <c r="G98" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H98" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I98" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J98">
         <v>-1</v>
       </c>
       <c r="K98" t="s">
-        <v>32</v>
-      </c>
-      <c r="R98" t="s">
-        <v>26</v>
-      </c>
-      <c r="S98" t="s">
-        <v>35</v>
-      </c>
-      <c r="U98" t="s">
-        <v>26</v>
-      </c>
-      <c r="X98">
+        <v>36</v>
+      </c>
+      <c r="P98" t="s">
+        <v>29</v>
+      </c>
+      <c r="W98" t="s">
+        <v>30</v>
+      </c>
+      <c r="X98" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB98">
         <v>9</v>
       </c>
     </row>
@@ -4777,7 +5050,7 @@
         <v>3</v>
       </c>
       <c r="C99" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -4789,33 +5062,36 @@
         <v>-39</v>
       </c>
       <c r="G99" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H99" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I99" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J99">
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>32</v>
-      </c>
-      <c r="R99" t="s">
-        <v>43</v>
-      </c>
-      <c r="S99" t="s">
-        <v>44</v>
-      </c>
-      <c r="U99" t="s">
-        <v>26</v>
-      </c>
-      <c r="V99" t="s">
-        <v>33</v>
-      </c>
-      <c r="X99">
+        <v>36</v>
+      </c>
+      <c r="P99" t="s">
+        <v>49</v>
+      </c>
+      <c r="W99" t="s">
+        <v>50</v>
+      </c>
+      <c r="X99" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA99" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB99">
         <v>9</v>
       </c>
     </row>
@@ -4827,7 +5103,7 @@
         <v>3</v>
       </c>
       <c r="C100" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -4839,30 +5115,33 @@
         <v>-39</v>
       </c>
       <c r="G100" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H100" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I100" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J100">
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>32</v>
-      </c>
-      <c r="R100" t="s">
-        <v>33</v>
-      </c>
-      <c r="S100" t="s">
-        <v>58</v>
-      </c>
-      <c r="U100" t="s">
-        <v>26</v>
-      </c>
-      <c r="X100">
+        <v>36</v>
+      </c>
+      <c r="P100" t="s">
+        <v>29</v>
+      </c>
+      <c r="W100" t="s">
+        <v>38</v>
+      </c>
+      <c r="X100" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z100" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB100">
         <v>9</v>
       </c>
     </row>
@@ -4874,7 +5153,7 @@
         <v>3</v>
       </c>
       <c r="C101" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -4886,15 +5165,15 @@
         <v>-39</v>
       </c>
       <c r="G101" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H101" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="I101" t="s">
-        <v>28</v>
-      </c>
-      <c r="X101">
+        <v>32</v>
+      </c>
+      <c r="AB101">
         <v>9</v>
       </c>
     </row>
@@ -4906,7 +5185,7 @@
         <v>3</v>
       </c>
       <c r="C102" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -4918,33 +5197,36 @@
         <v>-30</v>
       </c>
       <c r="G102" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H102" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I102" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J102">
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>38</v>
-      </c>
-      <c r="R102" t="s">
-        <v>26</v>
-      </c>
-      <c r="S102" t="s">
-        <v>58</v>
-      </c>
-      <c r="T102" t="s">
-        <v>79</v>
-      </c>
-      <c r="U102" t="s">
-        <v>33</v>
-      </c>
-      <c r="X102">
+        <v>43</v>
+      </c>
+      <c r="P102" t="s">
+        <v>37</v>
+      </c>
+      <c r="W102" t="s">
+        <v>30</v>
+      </c>
+      <c r="X102" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y102" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB102">
         <v>8</v>
       </c>
     </row>
@@ -4956,7 +5238,7 @@
         <v>3</v>
       </c>
       <c r="C103" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D103">
         <v>2</v>
@@ -4968,33 +5250,36 @@
         <v>-30</v>
       </c>
       <c r="G103" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H103" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I103" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J103">
         <v>33</v>
       </c>
       <c r="K103" t="s">
-        <v>32</v>
-      </c>
-      <c r="R103" t="s">
-        <v>26</v>
-      </c>
-      <c r="S103" t="s">
-        <v>52</v>
-      </c>
-      <c r="T103" t="s">
-        <v>47</v>
-      </c>
-      <c r="U103" t="s">
-        <v>33</v>
-      </c>
-      <c r="X103">
+        <v>36</v>
+      </c>
+      <c r="P103" t="s">
+        <v>37</v>
+      </c>
+      <c r="W103" t="s">
+        <v>30</v>
+      </c>
+      <c r="X103" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y103" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z103" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB103">
         <v>8</v>
       </c>
     </row>
@@ -5006,7 +5291,7 @@
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -5018,33 +5303,36 @@
         <v>37</v>
       </c>
       <c r="G104" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H104" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I104" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J104">
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>38</v>
-      </c>
-      <c r="R104" t="s">
-        <v>26</v>
-      </c>
-      <c r="S104" t="s">
-        <v>58</v>
-      </c>
-      <c r="T104" t="s">
-        <v>61</v>
-      </c>
-      <c r="U104" t="s">
-        <v>33</v>
-      </c>
-      <c r="X104">
+        <v>43</v>
+      </c>
+      <c r="P104" t="s">
+        <v>37</v>
+      </c>
+      <c r="W104" t="s">
+        <v>30</v>
+      </c>
+      <c r="X104" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y104" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z104" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB104">
         <v>8</v>
       </c>
     </row>
@@ -5056,7 +5344,7 @@
         <v>3</v>
       </c>
       <c r="C105" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D105">
         <v>2</v>
@@ -5068,33 +5356,36 @@
         <v>37</v>
       </c>
       <c r="G105" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H105" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I105" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J105">
         <v>7</v>
       </c>
       <c r="K105" t="s">
-        <v>32</v>
-      </c>
-      <c r="R105" t="s">
-        <v>26</v>
-      </c>
-      <c r="S105" t="s">
-        <v>58</v>
-      </c>
-      <c r="T105" t="s">
-        <v>79</v>
-      </c>
-      <c r="U105" t="s">
-        <v>26</v>
-      </c>
-      <c r="X105">
+        <v>36</v>
+      </c>
+      <c r="P105" t="s">
+        <v>37</v>
+      </c>
+      <c r="W105" t="s">
+        <v>30</v>
+      </c>
+      <c r="X105" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y105" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z105" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB105">
         <v>8</v>
       </c>
     </row>
@@ -5106,7 +5397,7 @@
         <v>3</v>
       </c>
       <c r="C106" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D106">
         <v>3</v>
@@ -5118,36 +5409,39 @@
         <v>30</v>
       </c>
       <c r="G106" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H106" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I106" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J106">
         <v>9</v>
       </c>
       <c r="K106" t="s">
-        <v>32</v>
-      </c>
-      <c r="R106" t="s">
-        <v>33</v>
-      </c>
-      <c r="S106" t="s">
-        <v>58</v>
-      </c>
-      <c r="T106" t="s">
-        <v>88</v>
-      </c>
-      <c r="U106" t="s">
-        <v>26</v>
-      </c>
-      <c r="V106" t="s">
-        <v>33</v>
-      </c>
-      <c r="X106">
+        <v>36</v>
+      </c>
+      <c r="P106" t="s">
+        <v>37</v>
+      </c>
+      <c r="W106" t="s">
+        <v>38</v>
+      </c>
+      <c r="X106" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y106" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z106" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA106" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB106">
         <v>8</v>
       </c>
     </row>
@@ -5159,7 +5453,7 @@
         <v>3</v>
       </c>
       <c r="C107" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -5171,33 +5465,36 @@
         <v>21</v>
       </c>
       <c r="G107" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H107" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I107" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J107">
         <v>2</v>
       </c>
       <c r="K107" t="s">
-        <v>38</v>
-      </c>
-      <c r="R107" t="s">
-        <v>26</v>
-      </c>
-      <c r="S107" t="s">
-        <v>49</v>
-      </c>
-      <c r="T107" t="s">
-        <v>89</v>
-      </c>
-      <c r="U107" t="s">
-        <v>26</v>
-      </c>
-      <c r="X107">
+        <v>43</v>
+      </c>
+      <c r="P107" t="s">
+        <v>72</v>
+      </c>
+      <c r="W107" t="s">
+        <v>30</v>
+      </c>
+      <c r="X107" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y107" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z107" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB107">
         <v>8</v>
       </c>
     </row>
@@ -5209,7 +5506,7 @@
         <v>3</v>
       </c>
       <c r="C108" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D108">
         <v>2</v>
@@ -5221,33 +5518,36 @@
         <v>19</v>
       </c>
       <c r="G108" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H108" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I108" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J108">
         <v>-3</v>
       </c>
       <c r="K108" t="s">
-        <v>38</v>
-      </c>
-      <c r="R108" t="s">
-        <v>26</v>
-      </c>
-      <c r="S108" t="s">
-        <v>90</v>
-      </c>
-      <c r="T108" t="s">
-        <v>89</v>
-      </c>
-      <c r="U108" t="s">
-        <v>33</v>
-      </c>
-      <c r="X108">
+        <v>43</v>
+      </c>
+      <c r="P108" t="s">
+        <v>72</v>
+      </c>
+      <c r="W108" t="s">
+        <v>30</v>
+      </c>
+      <c r="X108" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y108" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z108" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB108">
         <v>8</v>
       </c>
     </row>
@@ -5259,7 +5559,7 @@
         <v>4</v>
       </c>
       <c r="C109" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D109">
         <v>3</v>
@@ -5271,33 +5571,36 @@
         <v>22</v>
       </c>
       <c r="G109" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H109" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I109" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="J109">
         <v>1</v>
       </c>
       <c r="K109" t="s">
-        <v>38</v>
-      </c>
-      <c r="R109" t="s">
-        <v>26</v>
-      </c>
-      <c r="S109" t="s">
-        <v>44</v>
-      </c>
-      <c r="T109" t="s">
-        <v>76</v>
-      </c>
-      <c r="U109" t="s">
-        <v>33</v>
-      </c>
-      <c r="X109">
+        <v>43</v>
+      </c>
+      <c r="P109" t="s">
+        <v>37</v>
+      </c>
+      <c r="W109" t="s">
+        <v>30</v>
+      </c>
+      <c r="X109" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y109" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z109" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB109">
         <v>8</v>
       </c>
     </row>
@@ -5309,7 +5612,7 @@
         <v>4</v>
       </c>
       <c r="C110" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D110">
         <v>4</v>
@@ -5321,15 +5624,15 @@
         <v>21</v>
       </c>
       <c r="G110" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H110" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I110" t="s">
-        <v>91</v>
-      </c>
-      <c r="X110">
+        <v>103</v>
+      </c>
+      <c r="AB110">
         <v>8</v>
       </c>
     </row>
@@ -5341,7 +5644,7 @@
         <v>4</v>
       </c>
       <c r="C111" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -5353,30 +5656,33 @@
         <v>-20</v>
       </c>
       <c r="G111" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H111" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I111" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J111">
         <v>10</v>
       </c>
       <c r="K111" t="s">
-        <v>38</v>
-      </c>
-      <c r="R111" t="s">
-        <v>26</v>
-      </c>
-      <c r="U111" t="s">
-        <v>33</v>
-      </c>
-      <c r="V111" t="s">
-        <v>33</v>
-      </c>
-      <c r="X111">
+        <v>43</v>
+      </c>
+      <c r="P111" t="s">
+        <v>44</v>
+      </c>
+      <c r="W111" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z111" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA111" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB111">
         <v>10</v>
       </c>
     </row>
@@ -5388,7 +5694,7 @@
         <v>4</v>
       </c>
       <c r="C112" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -5400,30 +5706,33 @@
         <v>-30</v>
       </c>
       <c r="G112" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H112" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I112" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J112">
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>32</v>
-      </c>
-      <c r="R112" t="s">
-        <v>26</v>
-      </c>
-      <c r="S112" t="s">
-        <v>58</v>
-      </c>
-      <c r="U112" t="s">
-        <v>26</v>
-      </c>
-      <c r="X112">
+        <v>36</v>
+      </c>
+      <c r="P112" t="s">
+        <v>29</v>
+      </c>
+      <c r="W112" t="s">
+        <v>30</v>
+      </c>
+      <c r="X112" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z112" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB112">
         <v>10</v>
       </c>
     </row>
@@ -5435,7 +5744,7 @@
         <v>4</v>
       </c>
       <c r="C113" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D113">
         <v>2</v>
@@ -5447,30 +5756,33 @@
         <v>-30</v>
       </c>
       <c r="G113" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H113" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I113" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J113">
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>32</v>
-      </c>
-      <c r="R113" t="s">
-        <v>26</v>
-      </c>
-      <c r="S113" t="s">
-        <v>58</v>
-      </c>
-      <c r="U113" t="s">
-        <v>33</v>
-      </c>
-      <c r="X113">
+        <v>36</v>
+      </c>
+      <c r="P113" t="s">
+        <v>29</v>
+      </c>
+      <c r="W113" t="s">
+        <v>30</v>
+      </c>
+      <c r="X113" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z113" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB113">
         <v>10</v>
       </c>
     </row>
@@ -5482,7 +5794,7 @@
         <v>4</v>
       </c>
       <c r="C114" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D114">
         <v>3</v>
@@ -5494,30 +5806,33 @@
         <v>-30</v>
       </c>
       <c r="G114" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H114" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I114" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J114">
         <v>11</v>
       </c>
       <c r="K114" t="s">
-        <v>38</v>
-      </c>
-      <c r="R114" t="s">
-        <v>26</v>
-      </c>
-      <c r="S114" t="s">
-        <v>39</v>
-      </c>
-      <c r="U114" t="s">
-        <v>26</v>
-      </c>
-      <c r="X114">
+        <v>43</v>
+      </c>
+      <c r="P114" t="s">
+        <v>44</v>
+      </c>
+      <c r="W114" t="s">
+        <v>30</v>
+      </c>
+      <c r="X114" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z114" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB114">
         <v>10</v>
       </c>
     </row>
@@ -5529,7 +5844,7 @@
         <v>4</v>
       </c>
       <c r="C115" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -5541,30 +5856,33 @@
         <v>-41</v>
       </c>
       <c r="G115" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H115" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I115" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J115">
         <v>3</v>
       </c>
       <c r="K115" t="s">
-        <v>32</v>
-      </c>
-      <c r="R115" t="s">
-        <v>43</v>
-      </c>
-      <c r="S115" t="s">
-        <v>44</v>
-      </c>
-      <c r="U115" t="s">
-        <v>33</v>
-      </c>
-      <c r="X115">
+        <v>36</v>
+      </c>
+      <c r="P115" t="s">
+        <v>49</v>
+      </c>
+      <c r="W115" t="s">
+        <v>50</v>
+      </c>
+      <c r="X115" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z115" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB115">
         <v>10</v>
       </c>
     </row>
@@ -5576,7 +5894,7 @@
         <v>4</v>
       </c>
       <c r="C116" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D116">
         <v>2</v>
@@ -5588,30 +5906,33 @@
         <v>-44</v>
       </c>
       <c r="G116" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H116" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I116" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="J116">
         <v>56</v>
       </c>
       <c r="K116" t="s">
-        <v>38</v>
-      </c>
-      <c r="R116" t="s">
         <v>43</v>
       </c>
-      <c r="S116" t="s">
-        <v>44</v>
-      </c>
-      <c r="U116" t="s">
-        <v>33</v>
-      </c>
-      <c r="X116">
+      <c r="P116" t="s">
+        <v>49</v>
+      </c>
+      <c r="W116" t="s">
+        <v>50</v>
+      </c>
+      <c r="X116" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z116" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB116">
         <v>10</v>
       </c>
     </row>
@@ -5623,21 +5944,21 @@
         <v>4</v>
       </c>
       <c r="C117" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F117">
         <v>3</v>
       </c>
       <c r="G117" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H117" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="I117" t="s">
-        <v>65</v>
-      </c>
-      <c r="X117">
+        <v>76</v>
+      </c>
+      <c r="AB117">
         <v>10</v>
       </c>
     </row>
@@ -5649,19 +5970,19 @@
         <v>4</v>
       </c>
       <c r="C118" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F118">
         <v>-40</v>
       </c>
       <c r="G118" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H118" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="I118" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="119">
@@ -5672,7 +5993,7 @@
         <v>4</v>
       </c>
       <c r="C119" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -5684,33 +6005,36 @@
         <v>-20</v>
       </c>
       <c r="G119" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H119" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I119" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J119">
         <v>3</v>
       </c>
       <c r="K119" t="s">
-        <v>38</v>
-      </c>
-      <c r="R119" t="s">
-        <v>33</v>
-      </c>
-      <c r="S119" t="s">
-        <v>52</v>
-      </c>
-      <c r="T119" t="s">
-        <v>47</v>
-      </c>
-      <c r="U119" t="s">
-        <v>26</v>
-      </c>
-      <c r="X119">
+        <v>43</v>
+      </c>
+      <c r="P119" t="s">
+        <v>37</v>
+      </c>
+      <c r="W119" t="s">
+        <v>38</v>
+      </c>
+      <c r="X119" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y119" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z119" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB119">
         <v>9</v>
       </c>
     </row>
@@ -5722,7 +6046,7 @@
         <v>4</v>
       </c>
       <c r="C120" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D120">
         <v>2</v>
@@ -5734,36 +6058,39 @@
         <v>-23</v>
       </c>
       <c r="G120" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H120" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I120" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J120">
         <v>6</v>
       </c>
       <c r="K120" t="s">
-        <v>32</v>
-      </c>
-      <c r="R120" t="s">
-        <v>26</v>
-      </c>
-      <c r="S120" t="s">
-        <v>49</v>
-      </c>
-      <c r="T120" t="s">
-        <v>47</v>
-      </c>
-      <c r="U120" t="s">
-        <v>33</v>
-      </c>
-      <c r="V120" t="s">
-        <v>33</v>
-      </c>
-      <c r="X120">
+        <v>36</v>
+      </c>
+      <c r="P120" t="s">
+        <v>72</v>
+      </c>
+      <c r="W120" t="s">
+        <v>30</v>
+      </c>
+      <c r="X120" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y120" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z120" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA120" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB120">
         <v>9</v>
       </c>
     </row>
@@ -5775,7 +6102,7 @@
         <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D121">
         <v>3</v>
@@ -5787,33 +6114,36 @@
         <v>-29</v>
       </c>
       <c r="G121" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H121" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I121" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J121">
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>38</v>
-      </c>
-      <c r="R121" t="s">
-        <v>33</v>
-      </c>
-      <c r="S121" t="s">
-        <v>92</v>
-      </c>
-      <c r="T121" t="s">
-        <v>59</v>
-      </c>
-      <c r="U121" t="s">
-        <v>33</v>
-      </c>
-      <c r="X121">
+        <v>43</v>
+      </c>
+      <c r="P121" t="s">
+        <v>29</v>
+      </c>
+      <c r="W121" t="s">
+        <v>38</v>
+      </c>
+      <c r="X121" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y121" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z121" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB121">
         <v>9</v>
       </c>
     </row>
@@ -5825,7 +6155,7 @@
         <v>4</v>
       </c>
       <c r="C122" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D122">
         <v>4</v>
@@ -5837,15 +6167,15 @@
         <v>-29</v>
       </c>
       <c r="G122" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H122" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="I122" t="s">
-        <v>28</v>
-      </c>
-      <c r="X122">
+        <v>32</v>
+      </c>
+      <c r="AB122">
         <v>9</v>
       </c>
     </row>
@@ -5857,7 +6187,7 @@
         <v>4</v>
       </c>
       <c r="C123" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -5869,30 +6199,30 @@
         <v>40</v>
       </c>
       <c r="G123" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H123" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I123" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J123">
         <v>2</v>
       </c>
       <c r="K123" t="s">
-        <v>32</v>
-      </c>
-      <c r="R123" t="s">
-        <v>33</v>
-      </c>
-      <c r="S123" t="s">
-        <v>93</v>
-      </c>
-      <c r="U123" t="s">
-        <v>26</v>
-      </c>
-      <c r="X123">
+        <v>36</v>
+      </c>
+      <c r="W123" t="s">
+        <v>38</v>
+      </c>
+      <c r="X123" t="s">
+        <v>105</v>
+      </c>
+      <c r="Z123" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB123">
         <v>11</v>
       </c>
     </row>
@@ -5904,7 +6234,7 @@
         <v>4</v>
       </c>
       <c r="C124" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D124">
         <v>2</v>
@@ -5916,30 +6246,33 @@
         <v>38</v>
       </c>
       <c r="G124" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H124" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I124" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J124">
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>32</v>
-      </c>
-      <c r="R124" t="s">
-        <v>43</v>
-      </c>
-      <c r="S124" t="s">
-        <v>44</v>
-      </c>
-      <c r="U124" t="s">
-        <v>33</v>
-      </c>
-      <c r="X124">
+        <v>36</v>
+      </c>
+      <c r="P124" t="s">
+        <v>49</v>
+      </c>
+      <c r="W124" t="s">
+        <v>50</v>
+      </c>
+      <c r="X124" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z124" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB124">
         <v>11</v>
       </c>
     </row>
@@ -5951,7 +6284,7 @@
         <v>4</v>
       </c>
       <c r="C125" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D125">
         <v>2</v>
@@ -5963,27 +6296,30 @@
         <v>38</v>
       </c>
       <c r="G125" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H125" t="s">
+        <v>41</v>
+      </c>
+      <c r="I125" t="s">
+        <v>97</v>
+      </c>
+      <c r="K125" t="s">
         <v>36</v>
       </c>
-      <c r="I125" t="s">
-        <v>85</v>
-      </c>
-      <c r="K125" t="s">
-        <v>32</v>
-      </c>
-      <c r="R125" t="s">
-        <v>43</v>
-      </c>
-      <c r="S125" t="s">
-        <v>44</v>
-      </c>
-      <c r="U125" t="s">
-        <v>33</v>
-      </c>
-      <c r="X125">
+      <c r="P125" t="s">
+        <v>49</v>
+      </c>
+      <c r="W125" t="s">
+        <v>50</v>
+      </c>
+      <c r="X125" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z125" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB125">
         <v>11</v>
       </c>
     </row>
@@ -5995,7 +6331,7 @@
         <v>4</v>
       </c>
       <c r="C126" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -6007,33 +6343,36 @@
         <v>-21</v>
       </c>
       <c r="G126" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H126" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I126" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J126">
         <v>11</v>
       </c>
       <c r="K126" t="s">
-        <v>32</v>
-      </c>
-      <c r="R126" t="s">
-        <v>33</v>
-      </c>
-      <c r="S126" t="s">
-        <v>49</v>
-      </c>
-      <c r="T126" t="s">
-        <v>47</v>
-      </c>
-      <c r="U126" t="s">
-        <v>33</v>
-      </c>
-      <c r="X126">
+        <v>36</v>
+      </c>
+      <c r="P126" t="s">
+        <v>72</v>
+      </c>
+      <c r="W126" t="s">
+        <v>38</v>
+      </c>
+      <c r="X126" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y126" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z126" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB126">
         <v>10</v>
       </c>
     </row>
@@ -6045,7 +6384,7 @@
         <v>4</v>
       </c>
       <c r="C127" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -6057,33 +6396,36 @@
         <v>-32</v>
       </c>
       <c r="G127" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H127" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I127" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J127">
         <v>11</v>
       </c>
       <c r="K127" t="s">
-        <v>32</v>
-      </c>
-      <c r="R127" t="s">
-        <v>26</v>
-      </c>
-      <c r="S127" t="s">
-        <v>34</v>
-      </c>
-      <c r="T127" t="s">
-        <v>47</v>
-      </c>
-      <c r="U127" t="s">
-        <v>33</v>
-      </c>
-      <c r="X127">
+        <v>36</v>
+      </c>
+      <c r="P127" t="s">
+        <v>72</v>
+      </c>
+      <c r="W127" t="s">
+        <v>30</v>
+      </c>
+      <c r="X127" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y127" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z127" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB127">
         <v>10</v>
       </c>
     </row>
@@ -6095,7 +6437,7 @@
         <v>4</v>
       </c>
       <c r="C128" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -6107,33 +6449,36 @@
         <v>-43</v>
       </c>
       <c r="G128" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H128" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I128" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J128">
         <v>1</v>
       </c>
       <c r="K128" t="s">
-        <v>38</v>
-      </c>
-      <c r="R128" t="s">
-        <v>33</v>
-      </c>
-      <c r="S128" t="s">
-        <v>49</v>
-      </c>
-      <c r="T128" t="s">
-        <v>59</v>
-      </c>
-      <c r="U128" t="s">
-        <v>33</v>
-      </c>
-      <c r="X128">
+        <v>43</v>
+      </c>
+      <c r="P128" t="s">
+        <v>29</v>
+      </c>
+      <c r="W128" t="s">
+        <v>38</v>
+      </c>
+      <c r="X128" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y128" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z128" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB128">
         <v>10</v>
       </c>
     </row>
@@ -6145,7 +6490,7 @@
         <v>4</v>
       </c>
       <c r="C129" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D129">
         <v>2</v>
@@ -6157,33 +6502,36 @@
         <v>-44</v>
       </c>
       <c r="G129" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H129" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I129" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J129">
         <v>-1</v>
       </c>
       <c r="K129" t="s">
-        <v>38</v>
-      </c>
-      <c r="R129" t="s">
-        <v>26</v>
-      </c>
-      <c r="S129" t="s">
-        <v>58</v>
-      </c>
-      <c r="T129" t="s">
-        <v>60</v>
-      </c>
-      <c r="U129" t="s">
-        <v>26</v>
-      </c>
-      <c r="X129">
+        <v>43</v>
+      </c>
+      <c r="P129" t="s">
+        <v>37</v>
+      </c>
+      <c r="W129" t="s">
+        <v>30</v>
+      </c>
+      <c r="X129" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y129" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z129" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB129">
         <v>10</v>
       </c>
     </row>
@@ -6195,7 +6543,7 @@
         <v>4</v>
       </c>
       <c r="C130" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D130">
         <v>3</v>
@@ -6207,33 +6555,36 @@
         <v>-43</v>
       </c>
       <c r="G130" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H130" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I130" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J130">
         <v>0</v>
       </c>
       <c r="K130" t="s">
-        <v>38</v>
-      </c>
-      <c r="R130" t="s">
-        <v>26</v>
-      </c>
-      <c r="S130" t="s">
-        <v>44</v>
-      </c>
-      <c r="T130" t="s">
-        <v>71</v>
-      </c>
-      <c r="U130" t="s">
-        <v>26</v>
-      </c>
-      <c r="X130">
+        <v>43</v>
+      </c>
+      <c r="P130" t="s">
+        <v>29</v>
+      </c>
+      <c r="W130" t="s">
+        <v>30</v>
+      </c>
+      <c r="X130" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y130" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z130" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB130">
         <v>10</v>
       </c>
     </row>
@@ -6245,7 +6596,7 @@
         <v>4</v>
       </c>
       <c r="C131" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D131">
         <v>4</v>
@@ -6257,15 +6608,15 @@
         <v>-43</v>
       </c>
       <c r="G131" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H131" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="I131" t="s">
-        <v>94</v>
-      </c>
-      <c r="X131">
+        <v>106</v>
+      </c>
+      <c r="AB131">
         <v>10</v>
       </c>
     </row>
@@ -6277,7 +6628,7 @@
         <v>4</v>
       </c>
       <c r="C132" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D132">
         <v>1</v>
@@ -6289,33 +6640,36 @@
         <v>-5</v>
       </c>
       <c r="G132" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H132" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I132" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J132">
         <v>13</v>
       </c>
       <c r="K132" t="s">
-        <v>38</v>
-      </c>
-      <c r="R132" t="s">
-        <v>26</v>
-      </c>
-      <c r="S132" t="s">
-        <v>34</v>
-      </c>
-      <c r="U132" t="s">
-        <v>33</v>
-      </c>
-      <c r="V132" t="s">
-        <v>33</v>
-      </c>
-      <c r="X132">
+        <v>43</v>
+      </c>
+      <c r="P132" t="s">
+        <v>37</v>
+      </c>
+      <c r="W132" t="s">
+        <v>30</v>
+      </c>
+      <c r="X132" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z132" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA132" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB132">
         <v>12</v>
       </c>
     </row>
@@ -6327,7 +6681,7 @@
         <v>4</v>
       </c>
       <c r="C133" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D133">
         <v>1</v>
@@ -6339,30 +6693,33 @@
         <v>-18</v>
       </c>
       <c r="G133" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H133" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I133" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J133">
         <v>6</v>
       </c>
       <c r="K133" t="s">
-        <v>38</v>
-      </c>
-      <c r="R133" t="s">
-        <v>26</v>
-      </c>
-      <c r="S133" t="s">
-        <v>34</v>
-      </c>
-      <c r="U133" t="s">
-        <v>33</v>
-      </c>
-      <c r="X133">
+        <v>43</v>
+      </c>
+      <c r="P133" t="s">
+        <v>29</v>
+      </c>
+      <c r="W133" t="s">
+        <v>30</v>
+      </c>
+      <c r="X133" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z133" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB133">
         <v>12</v>
       </c>
     </row>
@@ -6374,7 +6731,7 @@
         <v>4</v>
       </c>
       <c r="C134" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D134">
         <v>2</v>
@@ -6386,18 +6743,18 @@
         <v>-24</v>
       </c>
       <c r="G134" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I134" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="J134">
         <v>0</v>
       </c>
       <c r="K134" t="s">
-        <v>32</v>
-      </c>
-      <c r="X134">
+        <v>36</v>
+      </c>
+      <c r="AB134">
         <v>12</v>
       </c>
     </row>
@@ -6409,7 +6766,7 @@
         <v>4</v>
       </c>
       <c r="C135" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D135">
         <v>2</v>
@@ -6421,30 +6778,33 @@
         <v>-24</v>
       </c>
       <c r="G135" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H135" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I135" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J135">
         <v>0</v>
       </c>
       <c r="K135" t="s">
-        <v>32</v>
-      </c>
-      <c r="R135" t="s">
-        <v>43</v>
-      </c>
-      <c r="S135" t="s">
-        <v>95</v>
-      </c>
-      <c r="U135" t="s">
-        <v>33</v>
-      </c>
-      <c r="X135">
+        <v>36</v>
+      </c>
+      <c r="P135" t="s">
+        <v>49</v>
+      </c>
+      <c r="W135" t="s">
+        <v>50</v>
+      </c>
+      <c r="X135" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z135" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB135">
         <v>12</v>
       </c>
     </row>
@@ -6456,7 +6816,7 @@
         <v>4</v>
       </c>
       <c r="C136" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D136">
         <v>3</v>
@@ -6468,18 +6828,18 @@
         <v>-24</v>
       </c>
       <c r="G136" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H136" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="I136" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K136" t="s">
-        <v>32</v>
-      </c>
-      <c r="X136">
+        <v>36</v>
+      </c>
+      <c r="AB136">
         <v>12</v>
       </c>
     </row>
@@ -6491,7 +6851,7 @@
         <v>4</v>
       </c>
       <c r="C137" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D137">
         <v>1</v>
@@ -6503,33 +6863,36 @@
         <v>-34</v>
       </c>
       <c r="G137" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H137" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I137" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J137">
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>38</v>
-      </c>
-      <c r="R137" t="s">
-        <v>26</v>
-      </c>
-      <c r="S137" t="s">
-        <v>44</v>
-      </c>
-      <c r="T137" t="s">
-        <v>76</v>
-      </c>
-      <c r="U137" t="s">
-        <v>33</v>
-      </c>
-      <c r="X137">
+        <v>43</v>
+      </c>
+      <c r="P137" t="s">
+        <v>29</v>
+      </c>
+      <c r="W137" t="s">
+        <v>30</v>
+      </c>
+      <c r="X137" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y137" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z137" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB137">
         <v>11</v>
       </c>
     </row>
@@ -6541,7 +6904,7 @@
         <v>4</v>
       </c>
       <c r="C138" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D138">
         <v>2</v>
@@ -6553,33 +6916,36 @@
         <v>-34</v>
       </c>
       <c r="G138" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H138" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I138" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J138">
         <v>0</v>
       </c>
       <c r="K138" t="s">
-        <v>38</v>
-      </c>
-      <c r="R138" t="s">
-        <v>26</v>
-      </c>
-      <c r="S138" t="s">
-        <v>58</v>
-      </c>
-      <c r="T138" t="s">
-        <v>96</v>
-      </c>
-      <c r="U138" t="s">
-        <v>33</v>
-      </c>
-      <c r="X138">
+        <v>43</v>
+      </c>
+      <c r="P138" t="s">
+        <v>37</v>
+      </c>
+      <c r="W138" t="s">
+        <v>30</v>
+      </c>
+      <c r="X138" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y138" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z138" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB138">
         <v>11</v>
       </c>
     </row>
@@ -6591,7 +6957,7 @@
         <v>4</v>
       </c>
       <c r="C139" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D139">
         <v>3</v>
@@ -6603,33 +6969,36 @@
         <v>-34</v>
       </c>
       <c r="G139" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H139" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I139" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J139">
         <v>22</v>
       </c>
       <c r="K139" t="s">
-        <v>32</v>
-      </c>
-      <c r="R139" t="s">
-        <v>26</v>
-      </c>
-      <c r="S139" t="s">
-        <v>35</v>
-      </c>
-      <c r="T139" t="s">
-        <v>97</v>
-      </c>
-      <c r="U139" t="s">
-        <v>33</v>
-      </c>
-      <c r="X139">
+        <v>36</v>
+      </c>
+      <c r="P139" t="s">
+        <v>37</v>
+      </c>
+      <c r="W139" t="s">
+        <v>30</v>
+      </c>
+      <c r="X139" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y139" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z139" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB139">
         <v>11</v>
       </c>
     </row>
@@ -6641,7 +7010,7 @@
         <v>4</v>
       </c>
       <c r="C140" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D140">
         <v>1</v>
@@ -6653,33 +7022,36 @@
         <v>44</v>
       </c>
       <c r="G140" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H140" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I140" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J140">
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>38</v>
-      </c>
-      <c r="R140" t="s">
-        <v>26</v>
-      </c>
-      <c r="S140" t="s">
-        <v>49</v>
-      </c>
-      <c r="T140" t="s">
-        <v>47</v>
-      </c>
-      <c r="U140" t="s">
-        <v>33</v>
-      </c>
-      <c r="X140">
+        <v>43</v>
+      </c>
+      <c r="P140" t="s">
+        <v>72</v>
+      </c>
+      <c r="W140" t="s">
+        <v>30</v>
+      </c>
+      <c r="X140" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y140" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z140" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB140">
         <v>11</v>
       </c>
     </row>
@@ -6691,7 +7063,7 @@
         <v>4</v>
       </c>
       <c r="C141" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D141">
         <v>2</v>
@@ -6703,33 +7075,36 @@
         <v>44</v>
       </c>
       <c r="G141" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H141" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I141" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J141">
         <v>11</v>
       </c>
       <c r="K141" t="s">
-        <v>32</v>
-      </c>
-      <c r="R141" t="s">
-        <v>26</v>
-      </c>
-      <c r="S141" t="s">
-        <v>44</v>
-      </c>
-      <c r="T141" t="s">
-        <v>76</v>
-      </c>
-      <c r="U141" t="s">
-        <v>33</v>
-      </c>
-      <c r="X141">
+        <v>36</v>
+      </c>
+      <c r="P141" t="s">
+        <v>37</v>
+      </c>
+      <c r="W141" t="s">
+        <v>30</v>
+      </c>
+      <c r="X141" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y141" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z141" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB141">
         <v>11</v>
       </c>
     </row>
@@ -6741,7 +7116,7 @@
         <v>4</v>
       </c>
       <c r="C142" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -6753,33 +7128,36 @@
         <v>33</v>
       </c>
       <c r="G142" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H142" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I142" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J142">
         <v>-2</v>
       </c>
       <c r="K142" t="s">
-        <v>38</v>
-      </c>
-      <c r="R142" t="s">
-        <v>26</v>
-      </c>
-      <c r="S142" t="s">
-        <v>35</v>
-      </c>
-      <c r="T142" t="s">
-        <v>70</v>
-      </c>
-      <c r="U142" t="s">
-        <v>33</v>
-      </c>
-      <c r="X142">
+        <v>43</v>
+      </c>
+      <c r="P142" t="s">
+        <v>37</v>
+      </c>
+      <c r="W142" t="s">
+        <v>30</v>
+      </c>
+      <c r="X142" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y142" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z142" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB142">
         <v>11</v>
       </c>
     </row>
@@ -6791,7 +7169,7 @@
         <v>4</v>
       </c>
       <c r="C143" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D143">
         <v>2</v>
@@ -6803,30 +7181,33 @@
         <v>35</v>
       </c>
       <c r="G143" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H143" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I143" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J143">
         <v>-5</v>
       </c>
       <c r="K143" t="s">
-        <v>38</v>
-      </c>
-      <c r="R143" t="s">
-        <v>33</v>
-      </c>
-      <c r="S143" t="s">
-        <v>44</v>
-      </c>
-      <c r="T143" t="s">
-        <v>76</v>
-      </c>
-      <c r="X143">
+        <v>43</v>
+      </c>
+      <c r="P143" t="s">
+        <v>37</v>
+      </c>
+      <c r="W143" t="s">
+        <v>38</v>
+      </c>
+      <c r="X143" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y143" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB143">
         <v>11</v>
       </c>
     </row>
@@ -6838,7 +7219,7 @@
         <v>4</v>
       </c>
       <c r="C144" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D144">
         <v>3</v>
@@ -6850,33 +7231,36 @@
         <v>40</v>
       </c>
       <c r="G144" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H144" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I144" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J144">
         <v>0</v>
       </c>
       <c r="K144" t="s">
-        <v>38</v>
-      </c>
-      <c r="R144" t="s">
-        <v>33</v>
-      </c>
-      <c r="S144" t="s">
-        <v>58</v>
-      </c>
-      <c r="T144" t="s">
-        <v>61</v>
-      </c>
-      <c r="U144" t="s">
-        <v>33</v>
-      </c>
-      <c r="X144">
+        <v>43</v>
+      </c>
+      <c r="P144" t="s">
+        <v>37</v>
+      </c>
+      <c r="W144" t="s">
+        <v>38</v>
+      </c>
+      <c r="X144" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y144" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z144" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB144">
         <v>11</v>
       </c>
     </row>
@@ -6888,7 +7272,7 @@
         <v>4</v>
       </c>
       <c r="C145" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D145">
         <v>4</v>
@@ -6900,36 +7284,39 @@
         <v>40</v>
       </c>
       <c r="G145" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H145" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I145" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J145">
         <v>0</v>
       </c>
       <c r="K145" t="s">
-        <v>38</v>
-      </c>
-      <c r="R145" t="s">
-        <v>33</v>
-      </c>
-      <c r="S145" t="s">
-        <v>44</v>
-      </c>
-      <c r="T145" t="s">
-        <v>61</v>
-      </c>
-      <c r="U145" t="s">
-        <v>26</v>
-      </c>
-      <c r="V145" t="s">
-        <v>33</v>
-      </c>
-      <c r="X145">
+        <v>43</v>
+      </c>
+      <c r="P145" t="s">
+        <v>29</v>
+      </c>
+      <c r="W145" t="s">
+        <v>38</v>
+      </c>
+      <c r="X145" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y145" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z145" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA145" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB145">
         <v>11</v>
       </c>
     </row>
